--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="771">
   <si>
     <t/>
   </si>
@@ -103,7 +103,7 @@
     <t>20129966</t>
   </si>
   <si>
-    <t>N/P MINUMAN LIME 330</t>
+    <t>N/P MNM LIME 330 ML</t>
   </si>
   <si>
     <t>20127835</t>
@@ -115,421 +115,415 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20138893</t>
-  </si>
-  <si>
-    <t>AMO DRMY STRAW 200ML</t>
+    <t>20065778</t>
+  </si>
+  <si>
+    <t>COCA COLA PET 390 ML</t>
+  </si>
+  <si>
+    <t>20128821</t>
+  </si>
+  <si>
+    <t>COCA COLA ZERO 390ML</t>
+  </si>
+  <si>
+    <t>20140260</t>
+  </si>
+  <si>
+    <t>CC.COLA ZERO VAN 390</t>
+  </si>
+  <si>
+    <t>20065779</t>
+  </si>
+  <si>
+    <t>SPRITE PET 390 ML</t>
+  </si>
+  <si>
+    <t>20130667</t>
+  </si>
+  <si>
+    <t>SPRITE ZERO LIME 390</t>
+  </si>
+  <si>
+    <t>20065780</t>
+  </si>
+  <si>
+    <t>FANTA STRW PET 390ML</t>
+  </si>
+  <si>
+    <t>20142491</t>
+  </si>
+  <si>
+    <t>SPRITE NIPIS MINT390</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20137093</t>
+  </si>
+  <si>
+    <t>FANTA ZERO STRAWB390</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20093993</t>
+  </si>
+  <si>
+    <t>FANTA GRAPE 390ML</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20123500</t>
+  </si>
+  <si>
+    <t>A&amp;W DRINK SARSA 250</t>
+  </si>
+  <si>
+    <t>20068089</t>
+  </si>
+  <si>
+    <t>GR.SANDS LMN&amp;GRP 250</t>
+  </si>
+  <si>
+    <t>10000107</t>
+  </si>
+  <si>
+    <t>GREEN SAND ORGNL 330</t>
+  </si>
+  <si>
+    <t>10033567</t>
+  </si>
+  <si>
+    <t>BINTANG ZERO KLG 330</t>
+  </si>
+  <si>
+    <t>20133709</t>
+  </si>
+  <si>
+    <t>POLARIS SARSAPRLA330</t>
+  </si>
+  <si>
+    <t>20002209</t>
+  </si>
+  <si>
+    <t>TEBS SPRK MIX FRT330</t>
+  </si>
+  <si>
+    <t>10037437</t>
+  </si>
+  <si>
+    <t>C/B PENY.STRAW 320</t>
+  </si>
+  <si>
+    <t>10003627</t>
+  </si>
+  <si>
+    <t>C/B PENY.ORANGE320</t>
+  </si>
+  <si>
+    <t>10004237</t>
+  </si>
+  <si>
+    <t>C/B PENY.LECI 320ML</t>
+  </si>
+  <si>
+    <t>10003842</t>
+  </si>
+  <si>
+    <t>C/B PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037144</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.LECI 320</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20037150</t>
+  </si>
+  <si>
+    <t>KAKI3 PENY.JAMBU 320</t>
+  </si>
+  <si>
+    <t>20037147</t>
+  </si>
+  <si>
+    <t>KAKI TIGA STRO 320ML</t>
+  </si>
+  <si>
+    <t>20045995</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK STRO 238</t>
+  </si>
+  <si>
+    <t>20053540</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK BTL 350</t>
+  </si>
+  <si>
+    <t>20122090</t>
+  </si>
+  <si>
+    <t>ADEM/S MD LMN TEA350</t>
+  </si>
+  <si>
+    <t>20083775</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK HR.T 320</t>
+  </si>
+  <si>
+    <t>20040276</t>
+  </si>
+  <si>
+    <t>ADEM SARI CK KLG 320</t>
+  </si>
+  <si>
+    <t>20071642</t>
+  </si>
+  <si>
+    <t>ADEMSARI CK SPRK 320</t>
+  </si>
+  <si>
+    <t>20069199</t>
+  </si>
+  <si>
+    <t>KAKI3 LMN.LM KLG 320</t>
+  </si>
+  <si>
+    <t>20142024</t>
+  </si>
+  <si>
+    <t>KK3 CLTPIA ML/ORG320</t>
+  </si>
+  <si>
+    <t>20045996</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK LECI 238</t>
+  </si>
+  <si>
+    <t>20046315</t>
+  </si>
+  <si>
+    <t>MINUTE M. NB STRW300</t>
+  </si>
+  <si>
+    <t>20046314</t>
+  </si>
+  <si>
+    <t>MINUTE M. NB ORG 300</t>
+  </si>
+  <si>
+    <t>20120499</t>
+  </si>
+  <si>
+    <t>K/A SIGNT STRONG 200</t>
+  </si>
+  <si>
+    <t>20089792</t>
+  </si>
+  <si>
+    <t>K/A DRNK BLK COFF200</t>
+  </si>
+  <si>
+    <t>20143469</t>
+  </si>
+  <si>
+    <t>GJAH K/TBRK GL BT200</t>
+  </si>
+  <si>
+    <t>20124713</t>
+  </si>
+  <si>
+    <t>LUWAK KOPI+GULA 220</t>
+  </si>
+  <si>
+    <t>20078206</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORGL 220ML</t>
+  </si>
+  <si>
+    <t>20123322</t>
+  </si>
+  <si>
+    <t>GOLDA CAPPUCCINO 200</t>
+  </si>
+  <si>
+    <t>20087542</t>
+  </si>
+  <si>
+    <t>GOLDA COFF.DOLCE 200</t>
+  </si>
+  <si>
+    <t>20143270</t>
+  </si>
+  <si>
+    <t>GOLDA AREN LATTE 200</t>
+  </si>
+  <si>
+    <t>20102789</t>
+  </si>
+  <si>
+    <t>ABC CHOCMLT COFF 180</t>
+  </si>
+  <si>
+    <t>20102790</t>
+  </si>
+  <si>
+    <t>ABC MILK COFFEE 180</t>
+  </si>
+  <si>
+    <t>20120904</t>
+  </si>
+  <si>
+    <t>KK BLACK AREN 220ML</t>
+  </si>
+  <si>
+    <t>20120906</t>
+  </si>
+  <si>
+    <t>KK MANTANCINO 220ML</t>
+  </si>
+  <si>
+    <t>20133409</t>
+  </si>
+  <si>
+    <t>KK CAFFE LATTE 200ML</t>
+  </si>
+  <si>
+    <t>20138168</t>
+  </si>
+  <si>
+    <t>KK CHEESE LATTEE 200</t>
+  </si>
+  <si>
+    <t>20138167</t>
+  </si>
+  <si>
+    <t>KK JPNS MATCHA 200</t>
+  </si>
+  <si>
+    <t>20129108</t>
+  </si>
+  <si>
+    <t>OATSDE COFFEE 200ML</t>
+  </si>
+  <si>
+    <t>20142499</t>
+  </si>
+  <si>
+    <t>OATSDE ESPR RST 240</t>
+  </si>
+  <si>
+    <t>20134557</t>
+  </si>
+  <si>
+    <t>OATSIDE CRML MCHT200</t>
+  </si>
+  <si>
+    <t>20129123</t>
+  </si>
+  <si>
+    <t>OATSDE CHOCO 200</t>
+  </si>
+  <si>
+    <t>20129102</t>
+  </si>
+  <si>
+    <t>OATSDE BR.BLEND 200</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>20045415</t>
+  </si>
+  <si>
+    <t>KOPIKO 78C 240ML</t>
+  </si>
+  <si>
+    <t>20109969</t>
+  </si>
+  <si>
+    <t>KOPIKO LUCKY DAY 180</t>
+  </si>
+  <si>
+    <t>20076770</t>
+  </si>
+  <si>
+    <t>G/DAY CAPPUCCINO 230</t>
+  </si>
+  <si>
+    <t>20045674</t>
+  </si>
+  <si>
+    <t>G/DAY F.MOCACINO 230</t>
+  </si>
+  <si>
+    <t>20045673</t>
+  </si>
+  <si>
+    <t>G/DAY TIRAMISU/B 230</t>
+  </si>
+  <si>
+    <t>20056193</t>
+  </si>
+  <si>
+    <t>GOOD DAY AVCDO/D 230</t>
+  </si>
+  <si>
+    <t>20132329</t>
+  </si>
+  <si>
+    <t>GOOD DAY GRVY CKS230</t>
+  </si>
+  <si>
+    <t>20132760</t>
+  </si>
+  <si>
+    <t>CAFINO RTD ESPRSO200</t>
+  </si>
+  <si>
+    <t>20132761</t>
+  </si>
+  <si>
+    <t>CAFINO RTD CPCINO200</t>
+  </si>
+  <si>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210 ML</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20138894</t>
-  </si>
-  <si>
-    <t>AMO FIZZY EASY 200ML</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20065778</t>
-  </si>
-  <si>
-    <t>COCA COLA PET 390 ML</t>
-  </si>
-  <si>
-    <t>20128821</t>
-  </si>
-  <si>
-    <t>COCA COLA ZERO 390ML</t>
-  </si>
-  <si>
-    <t>20140260</t>
-  </si>
-  <si>
-    <t>CC.COLA ZERO VAN 390</t>
-  </si>
-  <si>
-    <t>20065779</t>
-  </si>
-  <si>
-    <t>SPRITE PET 390 ML</t>
-  </si>
-  <si>
-    <t>20130667</t>
-  </si>
-  <si>
-    <t>SPRITE ZERO LIME 390</t>
-  </si>
-  <si>
-    <t>20065780</t>
-  </si>
-  <si>
-    <t>FANTA STRW PET 390ML</t>
-  </si>
-  <si>
-    <t>20142491</t>
-  </si>
-  <si>
-    <t>SPRITE NIPIS MINT390</t>
-  </si>
-  <si>
-    <t>20137093</t>
-  </si>
-  <si>
-    <t>FANTA ZERO STRAWB390</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20093993</t>
-  </si>
-  <si>
-    <t>FANTA GRAPE 390ML</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20123500</t>
-  </si>
-  <si>
-    <t>A&amp;W DRINK SARSA 250</t>
-  </si>
-  <si>
-    <t>20068089</t>
-  </si>
-  <si>
-    <t>GR.SANDS LMN&amp;GRP 250</t>
-  </si>
-  <si>
-    <t>10000107</t>
-  </si>
-  <si>
-    <t>GREEN SAND ORGNL 330</t>
-  </si>
-  <si>
-    <t>10033567</t>
-  </si>
-  <si>
-    <t>BINTANG ZERO KLG 330</t>
-  </si>
-  <si>
-    <t>20133709</t>
-  </si>
-  <si>
-    <t>POLARIS SARSAPRLA330</t>
-  </si>
-  <si>
-    <t>20002209</t>
-  </si>
-  <si>
-    <t>TEBS SPRK MIX FRT330</t>
-  </si>
-  <si>
-    <t>10037437</t>
-  </si>
-  <si>
-    <t>C/B PENY.STRAW 320</t>
-  </si>
-  <si>
-    <t>10003627</t>
-  </si>
-  <si>
-    <t>C/B PENY.ORANGE320</t>
-  </si>
-  <si>
-    <t>10004237</t>
-  </si>
-  <si>
-    <t>C/B PENY.LECI 320ML</t>
-  </si>
-  <si>
-    <t>10003842</t>
-  </si>
-  <si>
-    <t>C/B PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>20037144</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.LECI 320</t>
-  </si>
-  <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20037150</t>
-  </si>
-  <si>
-    <t>KAKI3 PENY.JAMBU 320</t>
-  </si>
-  <si>
-    <t>20037147</t>
-  </si>
-  <si>
-    <t>KAKI TIGA STRO 320ML</t>
-  </si>
-  <si>
-    <t>20045995</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK STRO 238</t>
-  </si>
-  <si>
-    <t>20053540</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK BTL 350</t>
-  </si>
-  <si>
-    <t>20122090</t>
-  </si>
-  <si>
-    <t>ADEM/S MD LMN TEA350</t>
-  </si>
-  <si>
-    <t>20083775</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK HR.T 320</t>
-  </si>
-  <si>
-    <t>20040276</t>
-  </si>
-  <si>
-    <t>ADEM SARI CK KLG 320</t>
-  </si>
-  <si>
-    <t>20071642</t>
-  </si>
-  <si>
-    <t>ADEMSARI CK SPRK 320</t>
-  </si>
-  <si>
-    <t>20069199</t>
-  </si>
-  <si>
-    <t>KAKI3 LMN.LM KLG 320</t>
-  </si>
-  <si>
-    <t>20142024</t>
-  </si>
-  <si>
-    <t>KK3 CLTPIA ML/ORG320</t>
-  </si>
-  <si>
-    <t>20045996</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK LECI 238</t>
-  </si>
-  <si>
-    <t>20046315</t>
-  </si>
-  <si>
-    <t>MINUTE M. NB STRW300</t>
-  </si>
-  <si>
-    <t>20046314</t>
-  </si>
-  <si>
-    <t>MINUTE M. NB ORG 300</t>
-  </si>
-  <si>
-    <t>20120499</t>
-  </si>
-  <si>
-    <t>K/A SIGNT STRONG 200</t>
-  </si>
-  <si>
-    <t>20089792</t>
-  </si>
-  <si>
-    <t>K/A DRNK BLK COFF200</t>
-  </si>
-  <si>
-    <t>20143469</t>
-  </si>
-  <si>
-    <t>GJAH K/TBRK GL BT200</t>
-  </si>
-  <si>
-    <t>20124713</t>
-  </si>
-  <si>
-    <t>LUWAK KOPI+GULA 220</t>
-  </si>
-  <si>
-    <t>20078206</t>
-  </si>
-  <si>
-    <t>LUWAK WHT ORGL 220ML</t>
-  </si>
-  <si>
-    <t>20123322</t>
-  </si>
-  <si>
-    <t>GOLDA CAPPUCCINO 200</t>
-  </si>
-  <si>
-    <t>20087542</t>
-  </si>
-  <si>
-    <t>GOLDA COFF.DOLCE 200</t>
-  </si>
-  <si>
-    <t>20102789</t>
-  </si>
-  <si>
-    <t>ABC CHOCMLT COFF 180</t>
-  </si>
-  <si>
-    <t>20102790</t>
-  </si>
-  <si>
-    <t>ABC MILK COFFEE 180</t>
-  </si>
-  <si>
-    <t>20120904</t>
-  </si>
-  <si>
-    <t>KK BLACK AREN 220ML</t>
-  </si>
-  <si>
-    <t>20120906</t>
-  </si>
-  <si>
-    <t>KK MANTANCINO 220ML</t>
-  </si>
-  <si>
-    <t>20133409</t>
-  </si>
-  <si>
-    <t>KK CAFFE LATTE 200ML</t>
-  </si>
-  <si>
-    <t>20138168</t>
-  </si>
-  <si>
-    <t>KK CHEESE LATTEE 200</t>
-  </si>
-  <si>
-    <t>20138167</t>
-  </si>
-  <si>
-    <t>KK JPNS MATCHA 200</t>
-  </si>
-  <si>
-    <t>20129108</t>
-  </si>
-  <si>
-    <t>OATSDE COFFEE 200ML</t>
-  </si>
-  <si>
-    <t>20142499</t>
-  </si>
-  <si>
-    <t>OATSDE ESPR RST 240</t>
-  </si>
-  <si>
-    <t>20134557</t>
-  </si>
-  <si>
-    <t>OATSIDE CRML MCHT200</t>
-  </si>
-  <si>
-    <t>20129123</t>
-  </si>
-  <si>
-    <t>OATSDE CHOCO 200</t>
-  </si>
-  <si>
-    <t>20129102</t>
-  </si>
-  <si>
-    <t>OATSDE BR.BLEND 200</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20045415</t>
-  </si>
-  <si>
-    <t>KOPIKO 78C 240ML</t>
-  </si>
-  <si>
-    <t>20109969</t>
-  </si>
-  <si>
-    <t>KOPIKO LUCKY DAY 180</t>
-  </si>
-  <si>
-    <t>20076770</t>
-  </si>
-  <si>
-    <t>G/DAY CAPPUCCINO 230</t>
-  </si>
-  <si>
-    <t>20045674</t>
-  </si>
-  <si>
-    <t>G/DAY F.MOCACINO 230</t>
-  </si>
-  <si>
-    <t>20045673</t>
-  </si>
-  <si>
-    <t>G/DAY TIRAMISU/B 230</t>
-  </si>
-  <si>
-    <t>20056193</t>
-  </si>
-  <si>
-    <t>GOOD DAY AVCDO/D 230</t>
-  </si>
-  <si>
-    <t>20132329</t>
-  </si>
-  <si>
-    <t>GOOD DAY GRVY CKS230</t>
-  </si>
-  <si>
-    <t>20132760</t>
-  </si>
-  <si>
-    <t>CAFINO RTD ESPRSO200</t>
-  </si>
-  <si>
-    <t>20132761</t>
-  </si>
-  <si>
-    <t>CAFINO RTD CPCINO200</t>
-  </si>
-  <si>
-    <t>20139577</t>
-  </si>
-  <si>
-    <t>PC AREN LATTE 210ML</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>20139578</t>
   </si>
   <si>
-    <t>PC GOLDN CARAMEL 210</t>
+    <t>PC GLDN CRML 210 ML</t>
   </si>
   <si>
     <t>20139576</t>
   </si>
   <si>
-    <t>PC CRMY CPUCCINO 210</t>
+    <t>PC CRMY CPCCN 210 ML</t>
   </si>
   <si>
     <t>20142601</t>
@@ -853,7 +847,7 @@
     <t>20035484</t>
   </si>
   <si>
-    <t>PUCUK/H TEH MLATI350</t>
+    <t>PUCUK TH MLTI 350 ML</t>
   </si>
   <si>
     <t>17</t>
@@ -862,7 +856,7 @@
     <t>20048155</t>
   </si>
   <si>
-    <t>PUCUK/H TEH L/SGR350</t>
+    <t>PUCUK TH L.S 350 ML</t>
   </si>
   <si>
     <t>20037565</t>
@@ -1291,7 +1285,7 @@
     <t>10007970</t>
   </si>
   <si>
-    <t>BUAVITA JAMBU SL 245</t>
+    <t>BUAVITA JAMBU 245 ML</t>
   </si>
   <si>
     <t>26</t>
@@ -1300,25 +1294,25 @@
     <t>10007974</t>
   </si>
   <si>
-    <t>BUAVITA LYCHEE SL245</t>
+    <t>BUAVITA LYCHE 245 ML</t>
   </si>
   <si>
     <t>10007971</t>
   </si>
   <si>
-    <t>BUAVITA ORANGE SL245</t>
+    <t>BUAVITA ORN 245 ML</t>
   </si>
   <si>
     <t>10007973</t>
   </si>
   <si>
-    <t>BUAVITA MANGGA 245ML</t>
+    <t>BUAVITA MGGA 245 ML</t>
   </si>
   <si>
     <t>10007972</t>
   </si>
   <si>
-    <t>BUAVITA JC APPLE 245</t>
+    <t>BUAVITA APPLE 245 ML</t>
   </si>
   <si>
     <t>20140324</t>
@@ -1684,7 +1678,7 @@
     <t>20103718</t>
   </si>
   <si>
-    <t>TJH KURMA SUSU KR189</t>
+    <t>TJH KRM SS KR 189 ML</t>
   </si>
   <si>
     <t>20136193</t>
@@ -2221,7 +2215,7 @@
     <t>20077499</t>
   </si>
   <si>
-    <t>PRISTINE 8.6+ BTL600</t>
+    <t>PRSTN 8 AIR B 600 ML</t>
   </si>
   <si>
     <t>20139699</t>
@@ -2329,16 +2323,7 @@
     <t>20005529</t>
   </si>
   <si>
-    <t>NESTLE PURE LIFE 600</t>
-  </si>
-  <si>
-    <t>20138035</t>
-  </si>
-  <si>
-    <t>CAFFINO OATMARIE 200</t>
-  </si>
-  <si>
-    <t>999</t>
+    <t>NESTLE MIN PL 600 ML</t>
   </si>
 </sst>
 </file>
@@ -2731,14 +2716,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F358"/>
+  <dimension ref="A1:F356"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="5" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2993,41 +2977,41 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="F14" s="1" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -3036,7 +3020,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -3044,10 +3028,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -3056,7 +3040,7 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -3064,10 +3048,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -3076,7 +3060,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -3084,10 +3068,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -3096,7 +3080,7 @@
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -3104,10 +3088,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -3116,7 +3100,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -3124,10 +3108,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -3136,7 +3120,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -3156,7 +3140,7 @@
         <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -3164,19 +3148,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -3193,21 +3177,21 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>59</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -3216,18 +3200,18 @@
         <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -3236,7 +3220,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>28</v>
@@ -3244,10 +3228,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -3256,18 +3240,18 @@
         <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -3276,7 +3260,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>28</v>
@@ -3284,19 +3268,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>33</v>
@@ -3304,30 +3288,30 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -3336,7 +3320,7 @@
         <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>33</v>
@@ -3344,10 +3328,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -3356,7 +3340,7 @@
         <v>17</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>33</v>
@@ -3364,10 +3348,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -3376,10 +3360,10 @@
         <v>17</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3396,10 +3380,10 @@
         <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3416,18 +3400,18 @@
         <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -3436,58 +3420,58 @@
         <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -3496,7 +3480,7 @@
         <v>20</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>28</v>
@@ -3504,10 +3488,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -3516,18 +3500,18 @@
         <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -3536,7 +3520,7 @@
         <v>20</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>28</v>
@@ -3544,10 +3528,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>96</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -3556,18 +3540,18 @@
         <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -3576,18 +3560,18 @@
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -3596,207 +3580,207 @@
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>82</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>82</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B53" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>28</v>
@@ -3804,79 +3788,79 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>28</v>
@@ -3884,19 +3868,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>28</v>
@@ -3904,19 +3888,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>28</v>
@@ -3924,19 +3908,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>134</v>
-      </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>28</v>
@@ -3944,19 +3928,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>28</v>
@@ -3964,19 +3948,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>28</v>
@@ -3984,19 +3968,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>140</v>
-      </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>28</v>
@@ -4004,19 +3988,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>142</v>
-      </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>28</v>
@@ -4024,19 +4008,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="C65" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>28</v>
@@ -4053,10 +4037,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>28</v>
@@ -4064,19 +4048,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>28</v>
@@ -4084,39 +4068,39 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>23</v>
@@ -4124,19 +4108,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>23</v>
@@ -4144,19 +4128,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>23</v>
@@ -4164,19 +4148,19 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>23</v>
@@ -4184,39 +4168,39 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>28</v>
@@ -4224,42 +4208,42 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="C75" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="E75" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>28</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F76" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4273,13 +4257,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>36</v>
+        <v>166</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4293,13 +4277,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4313,10 +4297,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>28</v>
@@ -4333,13 +4317,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -4353,13 +4337,13 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -4373,30 +4357,30 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>23</v>
@@ -4413,10 +4397,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>23</v>
@@ -4433,13 +4417,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4453,13 +4437,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -4473,10 +4457,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>23</v>
@@ -4493,10 +4477,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>23</v>
@@ -4513,10 +4497,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>23</v>
@@ -4533,13 +4517,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4553,10 +4537,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>28</v>
@@ -4573,30 +4557,30 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>183</v>
+        <v>202</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>33</v>
@@ -4613,13 +4597,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4633,13 +4617,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4653,10 +4637,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>28</v>
@@ -4673,13 +4657,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -4693,13 +4677,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4713,10 +4697,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>28</v>
@@ -4733,13 +4717,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4753,10 +4737,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -4773,30 +4757,30 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B103" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>225</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>28</v>
@@ -4813,10 +4797,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>28</v>
@@ -4833,10 +4817,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>28</v>
@@ -4853,10 +4837,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>28</v>
@@ -4873,10 +4857,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>28</v>
@@ -4893,10 +4877,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>28</v>
@@ -4913,10 +4897,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>28</v>
@@ -4933,33 +4917,33 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>28</v>
+        <v>166</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>242</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>36</v>
+        <v>166</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4973,13 +4957,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>36</v>
+        <v>166</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4993,13 +4977,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -5013,10 +4997,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>28</v>
@@ -5033,10 +5017,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>28</v>
@@ -5053,10 +5037,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>28</v>
@@ -5073,10 +5057,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>28</v>
@@ -5093,10 +5077,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>28</v>
@@ -5113,10 +5097,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>28</v>
@@ -5124,19 +5108,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B120" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>28</v>
@@ -5153,10 +5137,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>28</v>
@@ -5173,10 +5157,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>28</v>
@@ -5193,10 +5177,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>28</v>
@@ -5213,10 +5197,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>28</v>
@@ -5233,10 +5217,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>28</v>
@@ -5253,10 +5237,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>28</v>
@@ -5273,50 +5257,50 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>28</v>
+        <v>276</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>278</v>
+        <v>28</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>281</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>28</v>
@@ -5333,10 +5317,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>28</v>
@@ -5353,10 +5337,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>28</v>
@@ -5373,10 +5357,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>28</v>
@@ -5384,19 +5368,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>28</v>
@@ -5413,10 +5397,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>28</v>
@@ -5433,10 +5417,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>28</v>
@@ -5453,10 +5437,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>28</v>
@@ -5473,10 +5457,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>28</v>
@@ -5493,10 +5477,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>28</v>
@@ -5513,10 +5497,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>28</v>
@@ -5524,19 +5508,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B140" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>305</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>28</v>
@@ -5553,10 +5537,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>28</v>
@@ -5573,10 +5557,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>28</v>
@@ -5593,10 +5577,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>28</v>
@@ -5613,10 +5597,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>28</v>
@@ -5633,13 +5617,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -5653,10 +5637,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>33</v>
@@ -5673,33 +5657,33 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="B148" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>322</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -5713,10 +5697,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -5733,13 +5717,13 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -5753,10 +5737,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>28</v>
@@ -5773,10 +5757,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>28</v>
@@ -5793,10 +5777,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>28</v>
@@ -5813,13 +5797,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5833,30 +5817,30 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B156" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>28</v>
@@ -5873,10 +5857,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>28</v>
@@ -5893,10 +5877,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>28</v>
@@ -5913,13 +5897,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5933,10 +5917,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>23</v>
@@ -5953,10 +5937,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>23</v>
@@ -5973,13 +5957,13 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -5993,10 +5977,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>28</v>
@@ -6013,10 +5997,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>28</v>
@@ -6024,19 +6008,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>28</v>
@@ -6053,13 +6037,13 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -6073,13 +6057,13 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -6093,10 +6077,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>28</v>
@@ -6113,10 +6097,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>28</v>
@@ -6133,10 +6117,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>28</v>
@@ -6153,10 +6137,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>28</v>
@@ -6173,10 +6157,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>28</v>
@@ -6184,19 +6168,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B173" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>28</v>
@@ -6213,10 +6197,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>28</v>
@@ -6233,10 +6217,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>28</v>
@@ -6253,10 +6237,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>28</v>
@@ -6273,10 +6257,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>28</v>
@@ -6293,10 +6277,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>28</v>
@@ -6313,33 +6297,33 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="B180" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6353,10 +6337,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>28</v>
@@ -6373,33 +6357,33 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>28</v>
+        <v>395</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="B183" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6413,13 +6397,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>397</v>
+        <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6433,13 +6417,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6453,10 +6437,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>33</v>
@@ -6473,33 +6457,33 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>406</v>
       </c>
-      <c r="B188" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6513,13 +6497,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6533,13 +6517,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>33</v>
+        <v>77</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6553,13 +6537,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6573,13 +6557,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6593,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>23</v>
@@ -6613,13 +6597,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -6633,10 +6617,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>28</v>
@@ -6653,10 +6637,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>28</v>
@@ -6664,19 +6648,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="B197" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>28</v>
@@ -6693,10 +6677,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>28</v>
@@ -6713,10 +6697,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>28</v>
@@ -6733,10 +6717,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>28</v>
@@ -6753,10 +6737,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>28</v>
@@ -6773,10 +6757,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>28</v>
@@ -6793,10 +6777,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>28</v>
@@ -6813,10 +6797,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>28</v>
@@ -6833,10 +6817,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>28</v>
@@ -6853,10 +6837,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>427</v>
+        <v>446</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>28</v>
@@ -6864,19 +6848,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="B207" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="E207" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>28</v>
@@ -6893,10 +6877,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>28</v>
@@ -6913,10 +6897,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>28</v>
@@ -6933,10 +6917,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>28</v>
@@ -6953,10 +6937,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>28</v>
@@ -6973,10 +6957,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>28</v>
@@ -6993,10 +6977,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>28</v>
@@ -7013,13 +6997,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>28</v>
+        <v>166</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -7033,30 +7017,30 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B216" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="E216" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>28</v>
@@ -7073,10 +7057,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>28</v>
@@ -7093,10 +7077,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>28</v>
@@ -7113,10 +7097,10 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>28</v>
@@ -7133,10 +7117,10 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>28</v>
@@ -7153,10 +7137,10 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>28</v>
@@ -7173,13 +7157,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7193,13 +7177,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7213,10 +7197,10 @@
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>28</v>
@@ -7224,19 +7208,19 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D225" s="1" t="s">
         <v>484</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="C225" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>486</v>
-      </c>
       <c r="E225" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>28</v>
@@ -7253,10 +7237,10 @@
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>28</v>
@@ -7273,10 +7257,10 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>28</v>
@@ -7293,13 +7277,13 @@
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -7313,10 +7297,10 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>23</v>
@@ -7333,13 +7317,13 @@
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
@@ -7353,13 +7337,13 @@
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>36</v>
+        <v>166</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -7373,30 +7357,30 @@
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>486</v>
+        <v>501</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D233" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>503</v>
-      </c>
       <c r="E233" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>23</v>
@@ -7413,10 +7397,10 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>23</v>
@@ -7433,10 +7417,10 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>23</v>
@@ -7453,10 +7437,10 @@
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>23</v>
@@ -7473,13 +7457,13 @@
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
@@ -7493,10 +7477,10 @@
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>28</v>
@@ -7513,30 +7497,30 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D240" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="C240" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D240" s="1" t="s">
-        <v>518</v>
-      </c>
       <c r="E240" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>23</v>
@@ -7553,10 +7537,10 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>23</v>
@@ -7573,13 +7557,13 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -7593,33 +7577,33 @@
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>36</v>
+        <v>525</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>527</v>
+        <v>33</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7633,13 +7617,13 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7653,13 +7637,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7673,10 +7657,10 @@
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>33</v>
@@ -7693,10 +7677,10 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F248" s="1" t="s">
         <v>28</v>
@@ -7704,19 +7688,19 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D249" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="C249" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>538</v>
-      </c>
       <c r="E249" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>28</v>
@@ -7733,10 +7717,10 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>28</v>
@@ -7753,10 +7737,10 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>28</v>
@@ -7773,13 +7757,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7793,13 +7777,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7813,10 +7797,10 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7833,10 +7817,10 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7853,30 +7837,30 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="C257" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>555</v>
-      </c>
       <c r="E257" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>28</v>
@@ -7893,10 +7877,10 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>28</v>
@@ -7913,13 +7897,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7933,13 +7917,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7953,10 +7937,10 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>28</v>
@@ -7973,10 +7957,10 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>28</v>
@@ -7993,30 +7977,30 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D264" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="C264" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>570</v>
-      </c>
       <c r="E264" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>33</v>
@@ -8024,22 +8008,22 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B265" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="B265" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -8053,10 +8037,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>28</v>
@@ -8073,10 +8057,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>28</v>
@@ -8093,10 +8077,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>28</v>
@@ -8113,10 +8097,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>28</v>
@@ -8133,10 +8117,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>28</v>
@@ -8153,10 +8137,10 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>28</v>
@@ -8173,10 +8157,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>570</v>
+        <v>586</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>28</v>
@@ -8184,19 +8168,19 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D273" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="B273" s="1" t="s">
-        <v>587</v>
-      </c>
-      <c r="C273" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>588</v>
-      </c>
       <c r="E273" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>28</v>
@@ -8213,10 +8197,10 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>28</v>
@@ -8233,10 +8217,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>28</v>
@@ -8253,10 +8237,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>28</v>
@@ -8273,10 +8257,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>28</v>
@@ -8293,10 +8277,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>28</v>
@@ -8313,10 +8297,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>28</v>
@@ -8333,10 +8317,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>28</v>
@@ -8353,10 +8337,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>28</v>
@@ -8373,10 +8357,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>588</v>
+        <v>607</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>168</v>
+        <v>4</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>28</v>
@@ -8384,19 +8368,19 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>608</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D283" s="1" t="s">
         <v>607</v>
       </c>
-      <c r="B283" s="1" t="s">
-        <v>608</v>
-      </c>
-      <c r="C283" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>609</v>
-      </c>
       <c r="E283" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>28</v>
@@ -8413,10 +8397,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>28</v>
@@ -8433,10 +8417,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>28</v>
@@ -8453,10 +8437,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>28</v>
@@ -8473,10 +8457,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>28</v>
@@ -8493,33 +8477,33 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>28</v>
+        <v>620</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>622</v>
+        <v>28</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -8533,10 +8517,10 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>28</v>
@@ -8553,10 +8537,10 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>28</v>
@@ -8573,33 +8557,33 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>609</v>
+        <v>629</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>28</v>
+        <v>620</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D293" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="B293" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="C293" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="E293" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
@@ -8613,13 +8597,13 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8633,13 +8617,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8653,13 +8637,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8673,13 +8657,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8693,13 +8677,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8713,13 +8697,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8733,13 +8717,13 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8753,30 +8737,30 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>631</v>
+        <v>648</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>622</v>
+        <v>28</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="B302" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="C302" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D302" s="1" t="s">
         <v>648</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>650</v>
-      </c>
       <c r="E302" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>28</v>
@@ -8793,10 +8777,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>28</v>
@@ -8813,10 +8797,10 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>28</v>
@@ -8833,10 +8817,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>28</v>
@@ -8853,10 +8837,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>28</v>
@@ -8873,10 +8857,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>28</v>
@@ -8893,10 +8877,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>28</v>
@@ -8913,10 +8897,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>28</v>
@@ -8933,10 +8917,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>28</v>
@@ -8953,10 +8937,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>650</v>
+        <v>669</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>28</v>
@@ -8964,19 +8948,19 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B312" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="C312" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D312" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="C312" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D312" s="1" t="s">
-        <v>671</v>
-      </c>
       <c r="E312" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>28</v>
@@ -8993,10 +8977,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>28</v>
@@ -9013,10 +8997,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>28</v>
@@ -9033,10 +9017,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>28</v>
@@ -9053,10 +9037,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>28</v>
@@ -9073,10 +9057,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>28</v>
@@ -9093,10 +9077,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>28</v>
@@ -9113,10 +9097,10 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>28</v>
@@ -9133,10 +9117,10 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>671</v>
+        <v>688</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>28</v>
@@ -9144,19 +9128,19 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="B321" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="C321" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D321" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="B321" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="C321" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D321" s="1" t="s">
-        <v>690</v>
-      </c>
       <c r="E321" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>28</v>
@@ -9173,10 +9157,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>28</v>
@@ -9193,10 +9177,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>28</v>
@@ -9213,10 +9197,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>28</v>
@@ -9233,10 +9217,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>28</v>
@@ -9253,10 +9237,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>28</v>
@@ -9273,10 +9257,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>28</v>
@@ -9293,10 +9277,10 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>28</v>
@@ -9313,10 +9297,10 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>690</v>
+        <v>707</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>28</v>
@@ -9324,19 +9308,19 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="B330" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="C330" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D330" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="B330" s="1" t="s">
-        <v>708</v>
-      </c>
-      <c r="C330" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D330" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="E330" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>28</v>
@@ -9353,13 +9337,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9373,10 +9357,10 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>23</v>
@@ -9393,13 +9377,13 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -9413,10 +9397,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>28</v>
@@ -9433,10 +9417,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>28</v>
@@ -9453,10 +9437,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>28</v>
@@ -9473,10 +9457,10 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>28</v>
@@ -9493,10 +9477,10 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>59</v>
+        <v>144</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>28</v>
@@ -9513,33 +9497,33 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>709</v>
+        <v>728</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>147</v>
+        <v>4</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="C340" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D340" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="B340" s="1" t="s">
-        <v>729</v>
-      </c>
-      <c r="C340" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D340" s="1" t="s">
-        <v>730</v>
-      </c>
       <c r="E340" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9553,13 +9537,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9573,13 +9557,13 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -9593,13 +9577,13 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9613,10 +9597,10 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F344" s="1" t="s">
         <v>28</v>
@@ -9633,13 +9617,13 @@
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -9653,33 +9637,33 @@
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>23</v>
+        <v>743</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>745</v>
+        <v>33</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -9693,30 +9677,30 @@
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>730</v>
+        <v>748</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="C349" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D349" s="1" t="s">
         <v>748</v>
       </c>
-      <c r="B349" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="C349" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D349" s="1" t="s">
-        <v>750</v>
-      </c>
       <c r="E349" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F349" s="1" t="s">
         <v>28</v>
@@ -9733,13 +9717,13 @@
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>28</v>
+        <v>166</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -9753,152 +9737,112 @@
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B352" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>33</v>
+        <v>762</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="B354" s="1" t="s">
-        <v>762</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>763</v>
-      </c>
       <c r="E354" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B355" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A357" s="1" t="s">
-        <v>771</v>
-      </c>
-      <c r="B357" s="1" t="s">
-        <v>772</v>
-      </c>
-      <c r="C357" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D357" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="E357" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F357" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A358" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="B358" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="C358" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D358" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="E358" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F358" s="1" t="s">
         <v>28</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="775">
   <si>
     <t/>
   </si>
@@ -463,31 +463,31 @@
     <t>20076770</t>
   </si>
   <si>
-    <t>G/DAY CAPPUCCINO 230</t>
+    <t>G/DAY CAPPCIN 250 ML</t>
   </si>
   <si>
     <t>20045674</t>
   </si>
   <si>
-    <t>G/DAY F.MOCACINO 230</t>
+    <t>G/DAY F.MCACN 250 ML</t>
   </si>
   <si>
     <t>20045673</t>
   </si>
   <si>
-    <t>G/DAY TIRAMISU/B 230</t>
+    <t>G/DAY TRMSU/B 250 ML</t>
   </si>
   <si>
     <t>20056193</t>
   </si>
   <si>
-    <t>GOOD DAY AVCDO/D 230</t>
+    <t>G/DAY AVCDO/D 250 ML</t>
   </si>
   <si>
     <t>20132329</t>
   </si>
   <si>
-    <t>GOOD DAY GRVY CKS230</t>
+    <t>G/DAY GRY CKS 250 ML</t>
   </si>
   <si>
     <t>20132760</t>
@@ -1126,6 +1126,12 @@
     <t>COCO BIT HOK.MLN 350</t>
   </si>
   <si>
+    <t>20138959</t>
+  </si>
+  <si>
+    <t>IF COCONUT WTR 350ML</t>
+  </si>
+  <si>
     <t>20042848</t>
   </si>
   <si>
@@ -1417,12 +1423,6 @@
     <t>ISOPLUS COCO 350ML</t>
   </si>
   <si>
-    <t>20138959</t>
-  </si>
-  <si>
-    <t>IF COCONUT WTR 350ML</t>
-  </si>
-  <si>
     <t>20142818</t>
   </si>
   <si>
@@ -1447,333 +1447,357 @@
     <t>EWATER LEMON 380</t>
   </si>
   <si>
+    <t>20038726</t>
+  </si>
+  <si>
+    <t>NARAYA KDLAI BTL320</t>
+  </si>
+  <si>
+    <t>20048096</t>
+  </si>
+  <si>
+    <t>V-SOY SOYA BEAN 300</t>
+  </si>
+  <si>
+    <t>20136952</t>
+  </si>
+  <si>
+    <t>20135311</t>
+  </si>
+  <si>
+    <t>HYDROPL ISTNC JRK350</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20142358</t>
+  </si>
+  <si>
+    <t>POWRADE ACTIV WHT400</t>
+  </si>
+  <si>
+    <t>20142359</t>
+  </si>
+  <si>
+    <t>POWRADE ISOTN BLU400</t>
+  </si>
+  <si>
+    <t>20138837</t>
+  </si>
+  <si>
+    <t>MZONE COCO BOOST 500</t>
+  </si>
+  <si>
+    <t>20094167</t>
+  </si>
+  <si>
+    <t>MIZONE MOOD UP 500</t>
+  </si>
+  <si>
+    <t>20094164</t>
+  </si>
+  <si>
+    <t>MIZONE ACTIVE 500ML</t>
+  </si>
+  <si>
+    <t>20141600</t>
+  </si>
+  <si>
+    <t>IDM ISOTONC FRUIT350</t>
+  </si>
+  <si>
+    <t>20141601</t>
+  </si>
+  <si>
+    <t>IDM ISOTONC LYCHE350</t>
+  </si>
+  <si>
+    <t>20065248</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 350ML</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20118832</t>
+  </si>
+  <si>
+    <t>ION WATER BTL 500ML</t>
+  </si>
+  <si>
+    <t>20015838</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 350ML</t>
+  </si>
+  <si>
+    <t>20009722</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 500ML</t>
+  </si>
+  <si>
+    <t>20038777</t>
+  </si>
+  <si>
+    <t>POCARI SWEAT 900 ML</t>
+  </si>
+  <si>
+    <t>20019674</t>
+  </si>
+  <si>
+    <t>YOU C1000 ORG WTR500</t>
+  </si>
+  <si>
+    <t>20019673</t>
+  </si>
+  <si>
+    <t>YOU C1000 LMN WTR500</t>
+  </si>
+  <si>
+    <t>20057867</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 500ML</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20119876</t>
+  </si>
+  <si>
+    <t>HYDR.COCO VITA-D 330</t>
+  </si>
+  <si>
+    <t>20018435</t>
+  </si>
+  <si>
+    <t>HYDRO COCO 250ML</t>
+  </si>
+  <si>
+    <t>20115548</t>
+  </si>
+  <si>
+    <t>IDM COCONUT WTR 250</t>
+  </si>
+  <si>
+    <t>20089821</t>
+  </si>
+  <si>
+    <t>ORONAMIN C DRINK 120</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20115549</t>
+  </si>
+  <si>
+    <t>FIBE MINI 100ML</t>
+  </si>
+  <si>
+    <t>20142467</t>
+  </si>
+  <si>
+    <t>FIT ME UP RLX 160</t>
+  </si>
+  <si>
+    <t>20141124</t>
+  </si>
+  <si>
+    <t>REGEN ORANGE 300ML</t>
+  </si>
+  <si>
+    <t>20139550</t>
+  </si>
+  <si>
+    <t>REGEN LMN LIME 300ML</t>
+  </si>
+  <si>
+    <t>20009737</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK ORG140</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>10039897</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK LMN140</t>
+  </si>
+  <si>
+    <t>20032519</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK APL140</t>
+  </si>
+  <si>
+    <t>20115636</t>
+  </si>
+  <si>
+    <t>YOU C1000 DRK MGO140</t>
+  </si>
+  <si>
+    <t>20113135</t>
+  </si>
+  <si>
+    <t>AMUNIZER BTL 140ML</t>
+  </si>
+  <si>
+    <t>20048546</t>
+  </si>
+  <si>
+    <t>HEMAVITON C1000 330</t>
+  </si>
+  <si>
+    <t>20103178</t>
+  </si>
+  <si>
+    <t>HMVTON C1000 LSO 330</t>
+  </si>
+  <si>
+    <t>20103368</t>
+  </si>
+  <si>
+    <t>HMVTON C1000 LMN 330</t>
+  </si>
+  <si>
+    <t>20128794</t>
+  </si>
+  <si>
+    <t>NS/GOODNES KURMA 189</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20103718</t>
+  </si>
+  <si>
+    <t>TJH KRM SS KR 189 ML</t>
+  </si>
+  <si>
+    <t>20136193</t>
+  </si>
+  <si>
+    <t>SO GOOD SUSU STRL189</t>
+  </si>
+  <si>
+    <t>20133805</t>
+  </si>
+  <si>
+    <t>ENTRSL OLIVE STRL180</t>
+  </si>
+  <si>
+    <t>20134968</t>
+  </si>
+  <si>
+    <t>COLLAGENA SRL 189 ML</t>
+  </si>
+  <si>
+    <t>20140174</t>
+  </si>
+  <si>
+    <t>BEAR BRAND CLGEN 189</t>
+  </si>
+  <si>
+    <t>10004906</t>
+  </si>
+  <si>
+    <t>BEAR BRAND STERIL189</t>
+  </si>
+  <si>
+    <t>20107748</t>
+  </si>
+  <si>
+    <t>MILKU SUSU CKLT 200</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20107749</t>
+  </si>
+  <si>
+    <t>MILKU SUSU STRO 200</t>
+  </si>
+  <si>
+    <t>20141102</t>
+  </si>
+  <si>
+    <t>MILKU UHT MARIE 200</t>
+  </si>
+  <si>
+    <t>20134047</t>
+  </si>
+  <si>
+    <t>MILKU SUSU ORGNAL200</t>
+  </si>
+  <si>
+    <t>10003373</t>
+  </si>
+  <si>
+    <t>INDOMILK CAIR CHO190</t>
+  </si>
+  <si>
+    <t>10003426</t>
+  </si>
+  <si>
+    <t>INDOMILK CAIR STW190</t>
+  </si>
+  <si>
+    <t>20090314</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT F/C200ML</t>
+  </si>
+  <si>
+    <t>20091807</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT CKLT 200</t>
+  </si>
+  <si>
+    <t>20136644</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT MARSM200</t>
+  </si>
+  <si>
+    <t>20137977</t>
+  </si>
+  <si>
+    <t>DIAMOND UHT BBLGM200</t>
+  </si>
+  <si>
+    <t>20123171</t>
+  </si>
+  <si>
+    <t>LACTASOY MILK CLG250</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
     <t>20108987</t>
   </si>
   <si>
     <t>V-SOY MULTI-GRAIN200</t>
   </si>
   <si>
-    <t>20123171</t>
-  </si>
-  <si>
-    <t>LACTASOY MILK CLG250</t>
-  </si>
-  <si>
-    <t>20135311</t>
-  </si>
-  <si>
-    <t>HYDROPL ISTNC JRK350</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20142358</t>
-  </si>
-  <si>
-    <t>POWRADE ACTIV WHT400</t>
-  </si>
-  <si>
-    <t>20142359</t>
-  </si>
-  <si>
-    <t>POWRADE ISOTN BLU400</t>
-  </si>
-  <si>
-    <t>20138837</t>
-  </si>
-  <si>
-    <t>MZONE COCO BOOST 500</t>
-  </si>
-  <si>
-    <t>20094167</t>
-  </si>
-  <si>
-    <t>MIZONE MOOD UP 500</t>
-  </si>
-  <si>
-    <t>20094164</t>
-  </si>
-  <si>
-    <t>MIZONE ACTIVE 500ML</t>
-  </si>
-  <si>
-    <t>20141600</t>
-  </si>
-  <si>
-    <t>IDM ISOTONC FRUIT350</t>
-  </si>
-  <si>
-    <t>20141601</t>
-  </si>
-  <si>
-    <t>IDM ISOTONC LYCHE350</t>
-  </si>
-  <si>
-    <t>20065248</t>
-  </si>
-  <si>
-    <t>ION WATER BTL 350ML</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20118832</t>
-  </si>
-  <si>
-    <t>ION WATER BTL 500ML</t>
-  </si>
-  <si>
-    <t>20015838</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 350ML</t>
-  </si>
-  <si>
-    <t>20009722</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 500ML</t>
-  </si>
-  <si>
-    <t>20038777</t>
-  </si>
-  <si>
-    <t>POCARI SWEAT 900 ML</t>
-  </si>
-  <si>
-    <t>20019674</t>
-  </si>
-  <si>
-    <t>YOU C1000 ORG WTR500</t>
-  </si>
-  <si>
-    <t>20019673</t>
-  </si>
-  <si>
-    <t>YOU C1000 LMN WTR500</t>
-  </si>
-  <si>
-    <t>20057867</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 500ML</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20119876</t>
-  </si>
-  <si>
-    <t>HYDR.COCO VITA-D 330</t>
-  </si>
-  <si>
-    <t>20018435</t>
-  </si>
-  <si>
-    <t>HYDRO COCO 250ML</t>
-  </si>
-  <si>
-    <t>20115548</t>
-  </si>
-  <si>
-    <t>IDM COCONUT WTR 250</t>
-  </si>
-  <si>
-    <t>20089821</t>
-  </si>
-  <si>
-    <t>ORONAMIN C DRINK 120</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20115549</t>
-  </si>
-  <si>
-    <t>FIBE MINI 100ML</t>
-  </si>
-  <si>
-    <t>20142467</t>
-  </si>
-  <si>
-    <t>FIT ME UP RLX 160</t>
-  </si>
-  <si>
-    <t>20141124</t>
-  </si>
-  <si>
-    <t>REGEN ORANGE 300ML</t>
-  </si>
-  <si>
-    <t>20139550</t>
-  </si>
-  <si>
-    <t>REGEN LMN LIME 300ML</t>
-  </si>
-  <si>
-    <t>20009737</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK ORG140</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>10039897</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK LMN140</t>
-  </si>
-  <si>
-    <t>20032519</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK APL140</t>
-  </si>
-  <si>
-    <t>20115636</t>
-  </si>
-  <si>
-    <t>YOU C1000 DRK MGO140</t>
-  </si>
-  <si>
-    <t>20113135</t>
-  </si>
-  <si>
-    <t>AMUNIZER BTL 140ML</t>
-  </si>
-  <si>
-    <t>20048546</t>
-  </si>
-  <si>
-    <t>HEMAVITON C1000 330</t>
-  </si>
-  <si>
-    <t>20103178</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LSO 330</t>
-  </si>
-  <si>
-    <t>20103368</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LMN 330</t>
-  </si>
-  <si>
-    <t>20128794</t>
-  </si>
-  <si>
-    <t>NS/GOODNES KURMA 189</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20103718</t>
-  </si>
-  <si>
-    <t>TJH KRM SS KR 189 ML</t>
-  </si>
-  <si>
-    <t>20136193</t>
-  </si>
-  <si>
-    <t>SO GOOD SUSU STRL189</t>
-  </si>
-  <si>
-    <t>20133805</t>
-  </si>
-  <si>
-    <t>ENTRSL OLIVE STRL180</t>
-  </si>
-  <si>
-    <t>20134968</t>
-  </si>
-  <si>
-    <t>COLLAGENA SRL 189 ML</t>
-  </si>
-  <si>
-    <t>20140174</t>
-  </si>
-  <si>
-    <t>BEAR BRAND CLGEN 189</t>
-  </si>
-  <si>
-    <t>10004906</t>
-  </si>
-  <si>
-    <t>BEAR BRAND STERIL189</t>
-  </si>
-  <si>
-    <t>20136952</t>
-  </si>
-  <si>
-    <t>V-SOY SOYA BEAN 300</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20048096</t>
-  </si>
-  <si>
-    <t>20038726</t>
-  </si>
-  <si>
-    <t>NARAYA KDLAI BTL320</t>
-  </si>
-  <si>
-    <t>20107748</t>
-  </si>
-  <si>
-    <t>MILKU SUSU CKLT 200</t>
-  </si>
-  <si>
-    <t>20107749</t>
-  </si>
-  <si>
-    <t>MILKU SUSU STRO 200</t>
-  </si>
-  <si>
-    <t>20141102</t>
-  </si>
-  <si>
-    <t>MILKU UHT MARIE 200</t>
-  </si>
-  <si>
-    <t>20134047</t>
-  </si>
-  <si>
-    <t>MILKU SUSU ORGNAL200</t>
-  </si>
-  <si>
-    <t>10003373</t>
-  </si>
-  <si>
-    <t>INDOMILK CAIR CHO190</t>
-  </si>
-  <si>
-    <t>10003426</t>
-  </si>
-  <si>
-    <t>INDOMILK CAIR STW190</t>
-  </si>
-  <si>
     <t>10004443</t>
   </si>
   <si>
     <t>INDOMILK UHT CKL 180</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
     <t>10004442</t>
   </si>
   <si>
@@ -1804,28 +1828,22 @@
     <t>INDOMLK HK LYCHEE180</t>
   </si>
   <si>
-    <t>20091807</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT CKLT 200</t>
-  </si>
-  <si>
-    <t>20136644</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT MARSM200</t>
-  </si>
-  <si>
-    <t>20137977</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT BBLGM200</t>
-  </si>
-  <si>
-    <t>20090314</t>
-  </si>
-  <si>
-    <t>DIAMOND UHT F/C200ML</t>
+    <t>20142233</t>
+  </si>
+  <si>
+    <t>INDOMILK JAPANE M180</t>
+  </si>
+  <si>
+    <t>20143854</t>
+  </si>
+  <si>
+    <t>DMND MJ C/SHAKE200</t>
+  </si>
+  <si>
+    <t>20143855</t>
+  </si>
+  <si>
+    <t>DMND MJ MELON200</t>
   </si>
   <si>
     <t>20032643</t>
@@ -1954,7 +1972,7 @@
     <t>20025753</t>
   </si>
   <si>
-    <t>F/F L/FAT COK TPK225</t>
+    <t>FF L.F CKT TP 225 ML</t>
   </si>
   <si>
     <t>38</t>
@@ -1963,55 +1981,49 @@
     <t>20088875</t>
   </si>
   <si>
-    <t>FF SWT.DLGHT TPK 225</t>
+    <t>FF S.DLGHT TP 225 ML</t>
   </si>
   <si>
     <t>20070253</t>
   </si>
   <si>
-    <t>FF COCONUT TPK 225ML</t>
+    <t>FF COCONUT TP 225 ML</t>
   </si>
   <si>
     <t>20034079</t>
   </si>
   <si>
-    <t>F/FLAG COKLT TPK 225</t>
+    <t>F/FLAG CKT TP 225 ML</t>
   </si>
   <si>
     <t>20034078</t>
   </si>
   <si>
-    <t>F/FLAG STRWB TPK 225</t>
+    <t>F/FLAG STW TP 225 ML</t>
   </si>
   <si>
     <t>20034077</t>
   </si>
   <si>
-    <t>F/F FULL CRM TPK 225</t>
+    <t>F/FLAG FCM TP 225 ML</t>
   </si>
   <si>
     <t>20128754</t>
   </si>
   <si>
-    <t>FF SS.SEREAL CKL 225</t>
+    <t>F/FLAG SSR CK 225 ML</t>
   </si>
   <si>
     <t>20136769</t>
   </si>
   <si>
-    <t>F.FLAG UHT BERIS 225</t>
+    <t>F/FLAG  BRIES 225 ML</t>
   </si>
   <si>
     <t>20136768</t>
   </si>
   <si>
-    <t>F.FLAG UHT MATCH 225</t>
-  </si>
-  <si>
-    <t>20142233</t>
-  </si>
-  <si>
-    <t>INDOMILK JAPANE M180</t>
+    <t>FF UHT MATCH 225 ML</t>
   </si>
   <si>
     <t>20037974</t>
@@ -2269,7 +2281,7 @@
     <t>20142495</t>
   </si>
   <si>
-    <t>INDOMARET AIR MIN 1L</t>
+    <t>IDM AIR MINE BTL 1 L</t>
   </si>
   <si>
     <t>20069208</t>
@@ -2716,7 +2728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F356"/>
+  <dimension ref="A1:F358"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6157,10 +6169,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>28</v>
@@ -6168,19 +6180,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>28</v>
@@ -6197,10 +6209,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>28</v>
@@ -6217,10 +6229,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>28</v>
@@ -6237,10 +6249,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>28</v>
@@ -6257,10 +6269,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>28</v>
@@ -6277,10 +6289,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>28</v>
@@ -6297,33 +6309,33 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="B180" s="1" t="s">
+      <c r="C180" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="C180" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>388</v>
-      </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6337,10 +6349,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>28</v>
@@ -6357,33 +6369,33 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>395</v>
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F183" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6397,13 +6409,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>28</v>
+        <v>397</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6417,13 +6429,13 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6437,10 +6449,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>33</v>
@@ -6457,33 +6469,33 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>406</v>
+        <v>390</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B188" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="B188" s="1" t="s">
+      <c r="C188" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="C188" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>406</v>
-      </c>
       <c r="E188" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6497,13 +6509,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6517,13 +6529,13 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -6537,13 +6549,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -6557,13 +6569,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -6577,10 +6589,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>23</v>
@@ -6597,13 +6609,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -6617,10 +6629,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>28</v>
@@ -6637,10 +6649,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>28</v>
@@ -6648,19 +6660,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B197" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="B197" s="1" t="s">
+      <c r="C197" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="C197" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D197" s="1" t="s">
-        <v>425</v>
-      </c>
       <c r="E197" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>28</v>
@@ -6677,10 +6689,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>28</v>
@@ -6697,10 +6709,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>28</v>
@@ -6717,10 +6729,10 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>28</v>
@@ -6737,10 +6749,10 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>28</v>
@@ -6757,10 +6769,10 @@
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>28</v>
@@ -6777,10 +6789,10 @@
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>28</v>
@@ -6797,10 +6809,10 @@
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>28</v>
@@ -6817,10 +6829,10 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>28</v>
@@ -6837,10 +6849,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>28</v>
@@ -6848,19 +6860,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="B207" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B207" s="1" t="s">
+      <c r="C207" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C207" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>446</v>
-      </c>
       <c r="E207" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>28</v>
@@ -6877,10 +6889,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>28</v>
@@ -6897,10 +6909,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>28</v>
@@ -6917,10 +6929,10 @@
         <v>3</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>28</v>
@@ -6937,10 +6949,10 @@
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>28</v>
@@ -6957,10 +6969,10 @@
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>28</v>
@@ -6977,10 +6989,10 @@
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>28</v>
@@ -6997,13 +7009,13 @@
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -7017,30 +7029,30 @@
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>28</v>
+        <v>166</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B216" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="B216" s="1" t="s">
+      <c r="C216" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C216" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>465</v>
-      </c>
       <c r="E216" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>28</v>
@@ -7057,10 +7069,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>28</v>
@@ -7077,10 +7089,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>28</v>
@@ -7097,10 +7109,10 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>28</v>
@@ -7117,10 +7129,10 @@
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>28</v>
@@ -7137,10 +7149,10 @@
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>28</v>
@@ -7157,13 +7169,13 @@
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -7177,13 +7189,13 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -7191,36 +7203,36 @@
         <v>482</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D225" s="1" t="s">
         <v>485</v>
       </c>
-      <c r="B225" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="C225" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D225" s="1" t="s">
-        <v>484</v>
-      </c>
       <c r="E225" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>28</v>
@@ -7228,19 +7240,19 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>28</v>
@@ -7248,19 +7260,19 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B227" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="B227" s="1" t="s">
-        <v>490</v>
-      </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>28</v>
@@ -7268,39 +7280,39 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B228" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>492</v>
-      </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B229" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="B229" s="1" t="s">
-        <v>494</v>
-      </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>23</v>
@@ -7308,39 +7320,39 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="B230" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="B230" s="1" t="s">
-        <v>496</v>
-      </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="B231" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="B231" s="1" t="s">
-        <v>498</v>
-      </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>166</v>
@@ -7348,39 +7360,39 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="B232" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="B232" s="1" t="s">
-        <v>500</v>
-      </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>501</v>
+        <v>485</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D233" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="B233" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="C233" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>501</v>
-      </c>
       <c r="E233" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>23</v>
@@ -7388,19 +7400,19 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="B234" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="B234" s="1" t="s">
-        <v>505</v>
-      </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>23</v>
@@ -7408,19 +7420,19 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="B235" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="B235" s="1" t="s">
-        <v>507</v>
-      </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>23</v>
@@ -7428,19 +7440,19 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="B236" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>23</v>
@@ -7448,39 +7460,39 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="B237" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="B237" s="1" t="s">
-        <v>511</v>
-      </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="B238" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="B238" s="1" t="s">
-        <v>513</v>
-      </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>28</v>
@@ -7488,39 +7500,39 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="B239" s="1" t="s">
         <v>514</v>
       </c>
-      <c r="B239" s="1" t="s">
-        <v>515</v>
-      </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D240" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="B240" s="1" t="s">
-        <v>518</v>
-      </c>
-      <c r="C240" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D240" s="1" t="s">
-        <v>516</v>
-      </c>
       <c r="E240" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>23</v>
@@ -7528,19 +7540,19 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="B241" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="B241" s="1" t="s">
-        <v>520</v>
-      </c>
       <c r="C241" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F241" s="1" t="s">
         <v>23</v>
@@ -7548,119 +7560,119 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="B242" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="B242" s="1" t="s">
-        <v>522</v>
-      </c>
       <c r="C242" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="B243" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="B243" s="1" t="s">
-        <v>524</v>
-      </c>
       <c r="C243" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>525</v>
+        <v>166</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F244" s="1" t="s">
         <v>526</v>
-      </c>
-      <c r="B244" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="C244" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D244" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="E244" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F244" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B245" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="B245" s="1" t="s">
-        <v>529</v>
-      </c>
       <c r="C245" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="B246" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="B246" s="1" t="s">
-        <v>531</v>
-      </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="B247" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="B247" s="1" t="s">
-        <v>533</v>
-      </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>33</v>
@@ -7668,39 +7680,39 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B248" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="B248" s="1" t="s">
-        <v>535</v>
-      </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>536</v>
+        <v>517</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D249" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="C249" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>536</v>
-      </c>
       <c r="E249" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>28</v>
@@ -7708,19 +7720,19 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="B250" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="B250" s="1" t="s">
-        <v>540</v>
-      </c>
       <c r="C250" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>28</v>
@@ -7728,19 +7740,19 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>542</v>
-      </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>28</v>
@@ -7748,59 +7760,59 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="B252" s="1" t="s">
-        <v>544</v>
-      </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="B253" s="1" t="s">
         <v>545</v>
       </c>
-      <c r="B253" s="1" t="s">
-        <v>546</v>
-      </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="B254" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="B254" s="1" t="s">
-        <v>548</v>
-      </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7808,19 +7820,19 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B255" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="B255" s="1" t="s">
-        <v>550</v>
-      </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7828,39 +7840,39 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="B256" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="B256" s="1" t="s">
-        <v>552</v>
-      </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>553</v>
+        <v>537</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="C257" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>553</v>
-      </c>
       <c r="E257" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>28</v>
@@ -7868,19 +7880,19 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B258" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="B258" s="1" t="s">
-        <v>557</v>
-      </c>
       <c r="C258" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>28</v>
@@ -7888,59 +7900,59 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B259" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>559</v>
-      </c>
       <c r="C259" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B260" s="1" t="s">
         <v>560</v>
       </c>
-      <c r="B260" s="1" t="s">
-        <v>561</v>
-      </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B261" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="B261" s="1" t="s">
-        <v>563</v>
-      </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>28</v>
@@ -7948,19 +7960,19 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B262" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B262" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>28</v>
@@ -7968,42 +7980,42 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="B263" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="B263" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D264" s="1" t="s">
         <v>569</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="C264" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>568</v>
-      </c>
       <c r="E264" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -8017,10 +8029,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>28</v>
@@ -8037,10 +8049,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>28</v>
@@ -8057,10 +8069,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>28</v>
@@ -8077,10 +8089,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>28</v>
@@ -8097,10 +8109,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>28</v>
@@ -8117,10 +8129,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>28</v>
@@ -8137,10 +8149,10 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>28</v>
@@ -8157,10 +8169,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>586</v>
+        <v>569</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>28</v>
@@ -8168,19 +8180,19 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B273" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="B273" s="1" t="s">
-        <v>588</v>
-      </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>586</v>
+        <v>569</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>8</v>
+        <v>144</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>28</v>
@@ -8188,19 +8200,19 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B274" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="B274" s="1" t="s">
+      <c r="C274" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D274" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="C274" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D274" s="1" t="s">
-        <v>586</v>
-      </c>
       <c r="E274" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>28</v>
@@ -8217,13 +8229,13 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -8237,10 +8249,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>28</v>
@@ -8257,10 +8269,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>28</v>
@@ -8277,10 +8289,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>28</v>
@@ -8297,10 +8309,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>28</v>
@@ -8317,10 +8329,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>28</v>
@@ -8337,10 +8349,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>165</v>
+        <v>51</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>28</v>
@@ -8357,10 +8369,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>28</v>
@@ -8368,19 +8380,19 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
+        <v>607</v>
+      </c>
+      <c r="B283" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="B283" s="1" t="s">
-        <v>609</v>
-      </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>8</v>
+        <v>144</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>28</v>
@@ -8388,19 +8400,19 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B284" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="B284" s="1" t="s">
-        <v>611</v>
-      </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>28</v>
@@ -8408,19 +8420,19 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="B285" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="B285" s="1" t="s">
+      <c r="C285" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D285" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="C285" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>607</v>
-      </c>
       <c r="E285" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>28</v>
@@ -8437,10 +8449,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>28</v>
@@ -8457,10 +8469,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>28</v>
@@ -8477,30 +8489,30 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>620</v>
+        <v>28</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B289" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="B289" s="1" t="s">
-        <v>622</v>
-      </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>28</v>
@@ -8508,19 +8520,19 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="B290" s="1" t="s">
         <v>623</v>
       </c>
-      <c r="B290" s="1" t="s">
-        <v>624</v>
-      </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>28</v>
@@ -8528,22 +8540,22 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B291" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="B291" s="1" t="s">
+      <c r="C291" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F291" s="1" t="s">
         <v>626</v>
-      </c>
-      <c r="C291" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D291" s="1" t="s">
-        <v>607</v>
-      </c>
-      <c r="E291" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F291" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8557,73 +8569,73 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>620</v>
+        <v>28</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B293" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="B293" s="1" t="s">
-        <v>631</v>
-      </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>620</v>
+        <v>28</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="B294" s="1" t="s">
         <v>632</v>
       </c>
-      <c r="B294" s="1" t="s">
-        <v>633</v>
-      </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>11</v>
+        <v>144</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>620</v>
+        <v>28</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="B295" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="B295" s="1" t="s">
+      <c r="C295" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D295" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="C295" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>629</v>
-      </c>
       <c r="E295" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8637,13 +8649,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8657,13 +8669,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8677,13 +8689,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8697,13 +8709,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8717,13 +8729,13 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8737,70 +8749,70 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>28</v>
+        <v>626</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B302" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="B302" s="1" t="s">
-        <v>650</v>
-      </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>28</v>
+        <v>626</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B303" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="B303" s="1" t="s">
-        <v>652</v>
-      </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>28</v>
+        <v>626</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="B304" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="B304" s="1" t="s">
+      <c r="C304" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D304" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="C304" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>648</v>
-      </c>
       <c r="E304" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>28</v>
@@ -8817,10 +8829,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>28</v>
@@ -8837,10 +8849,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>28</v>
@@ -8857,10 +8869,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>28</v>
@@ -8877,10 +8889,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>28</v>
@@ -8897,10 +8909,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>28</v>
@@ -8917,10 +8929,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>144</v>
+        <v>48</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>28</v>
@@ -8937,10 +8949,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>28</v>
@@ -8948,19 +8960,19 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="B312" s="1" t="s">
-        <v>671</v>
-      </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>28</v>
@@ -8968,19 +8980,19 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B313" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="B313" s="1" t="s">
+      <c r="C313" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D313" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="C313" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="E313" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>28</v>
@@ -8997,10 +9009,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>28</v>
@@ -9017,10 +9029,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>28</v>
@@ -9037,10 +9049,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>28</v>
@@ -9057,10 +9069,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>28</v>
@@ -9077,10 +9089,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>28</v>
@@ -9097,10 +9109,10 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>28</v>
@@ -9117,10 +9129,10 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>688</v>
+        <v>673</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>28</v>
@@ -9128,19 +9140,19 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="B321" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="B321" s="1" t="s">
-        <v>690</v>
-      </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>688</v>
+        <v>673</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>28</v>
@@ -9148,19 +9160,19 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B322" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="B322" s="1" t="s">
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="C322" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>688</v>
-      </c>
       <c r="E322" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>28</v>
@@ -9177,10 +9189,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>28</v>
@@ -9197,10 +9209,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>28</v>
@@ -9217,10 +9229,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>28</v>
@@ -9237,10 +9249,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>28</v>
@@ -9257,10 +9269,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>28</v>
@@ -9277,10 +9289,10 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>28</v>
@@ -9297,10 +9309,10 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>28</v>
@@ -9308,19 +9320,19 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B330" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="B330" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>707</v>
+        <v>692</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>28</v>
@@ -9328,22 +9340,22 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B331" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="B331" s="1" t="s">
+      <c r="C331" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D331" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="C331" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>707</v>
-      </c>
       <c r="E331" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -9357,13 +9369,13 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -9377,13 +9389,13 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
@@ -9397,13 +9409,13 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -9417,10 +9429,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>28</v>
@@ -9437,10 +9449,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>28</v>
@@ -9457,10 +9469,10 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>28</v>
@@ -9477,10 +9489,10 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>144</v>
+        <v>51</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>28</v>
@@ -9497,53 +9509,53 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="F339" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B340" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="B340" s="1" t="s">
-        <v>730</v>
-      </c>
       <c r="C340" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>728</v>
+        <v>711</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>8</v>
+        <v>144</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B341" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="B341" s="1" t="s">
+      <c r="C341" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D341" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="C341" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>728</v>
-      </c>
       <c r="E341" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9557,10 +9569,10 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>23</v>
@@ -9577,10 +9589,10 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>28</v>
@@ -9597,13 +9609,13 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -9617,13 +9629,13 @@
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -9637,93 +9649,93 @@
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>743</v>
+        <v>28</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="B347" s="1" t="s">
-        <v>745</v>
-      </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="B348" s="1" t="s">
+      <c r="C348" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="E348" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F348" s="1" t="s">
         <v>747</v>
-      </c>
-      <c r="C348" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D348" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="E348" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F348" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="B349" s="1" t="s">
-        <v>750</v>
-      </c>
       <c r="C349" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>748</v>
+        <v>732</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="B350" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="B350" s="1" t="s">
+      <c r="C350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D350" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="C350" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D350" s="1" t="s">
-        <v>748</v>
-      </c>
       <c r="E350" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -9737,10 +9749,10 @@
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F351" s="1" t="s">
         <v>28</v>
@@ -9748,101 +9760,141 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B352" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="B352" s="1" t="s">
-        <v>757</v>
-      </c>
       <c r="C352" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>33</v>
+        <v>166</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B353" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D353" s="1" t="s">
         <v>759</v>
-      </c>
-      <c r="B353" s="1" t="s">
-        <v>760</v>
-      </c>
-      <c r="C353" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D353" s="1" t="s">
-        <v>761</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>762</v>
+        <v>28</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>765</v>
+        <v>33</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="E355" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F355" s="1" t="s">
         <v>766</v>
-      </c>
-      <c r="B355" s="1" t="s">
-        <v>767</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="E355" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F355" s="1" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="E356" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F356" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="B356" s="1" t="s">
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="C356" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D356" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="E356" s="1" t="s">
+      <c r="B357" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="C357" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="E357" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F357" s="1" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="E358" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F356" s="1" t="s">
+      <c r="F358" s="1" t="s">
         <v>28</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2148" uniqueCount="775">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="773">
   <si>
     <t/>
   </si>
@@ -1234,7 +1234,7 @@
     <t>10008887</t>
   </si>
   <si>
-    <t>ULTRA KCNG HIJAU 250</t>
+    <t>ULTRA K.HIJAU 250 ML</t>
   </si>
   <si>
     <t>25</t>
@@ -1336,7 +1336,7 @@
     <t>10007385</t>
   </si>
   <si>
-    <t>ULTRA SR ASAM SLM250</t>
+    <t>ULTRA S.ASM S 250 ML</t>
   </si>
   <si>
     <t>20136649</t>
@@ -1579,12 +1579,6 @@
     <t>HYDRO COCO 250ML</t>
   </si>
   <si>
-    <t>20115548</t>
-  </si>
-  <si>
-    <t>IDM COCONUT WTR 250</t>
-  </si>
-  <si>
     <t>20089821</t>
   </si>
   <si>
@@ -1795,25 +1789,25 @@
     <t>10004443</t>
   </si>
   <si>
-    <t>INDOMILK UHT CKL 180</t>
+    <t>INDOMLK UHT CO 180 G</t>
   </si>
   <si>
     <t>10004442</t>
   </si>
   <si>
-    <t>INDOMLK UHT STRW 180</t>
+    <t>INDOMLK UHT ST 180 G</t>
   </si>
   <si>
     <t>20070569</t>
   </si>
   <si>
-    <t>INDOMLK BANANA 180</t>
+    <t>INDOMLK BANANA 180 G</t>
   </si>
   <si>
     <t>20127735</t>
   </si>
   <si>
-    <t>INDMLK DLGNA COFF180</t>
+    <t>INDOMLK DL COF 180 G</t>
   </si>
   <si>
     <t>20125062</t>
@@ -1831,7 +1825,7 @@
     <t>20142233</t>
   </si>
   <si>
-    <t>INDOMILK JAPANE M180</t>
+    <t>INDOMLK JPN M 180 G</t>
   </si>
   <si>
     <t>20143854</t>
@@ -1882,13 +1876,13 @@
     <t>20138916</t>
   </si>
   <si>
-    <t>CIMORY THAI TEA 250</t>
+    <t>CIMORY THAI TEA 225</t>
   </si>
   <si>
     <t>20136951</t>
   </si>
   <si>
-    <t>CMORY UHT MATCHA 250</t>
+    <t>CMORY UHT MATCHA 225</t>
   </si>
   <si>
     <t>RT,(E-0.5B)</t>
@@ -1897,76 +1891,76 @@
     <t>20140795</t>
   </si>
   <si>
+    <t>CMRY UHT NSG CHOC225</t>
+  </si>
+  <si>
+    <t>20140794</t>
+  </si>
+  <si>
+    <t>CMRY UHT NSG MRIE225</t>
+  </si>
+  <si>
+    <t>20140793</t>
+  </si>
+  <si>
+    <t>CMRY UHT NSG MCHA225</t>
+  </si>
+  <si>
+    <t>20122822</t>
+  </si>
+  <si>
+    <t>CMORY UHT MARIE 225</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20115187</t>
+  </si>
+  <si>
+    <t>CMORY UHT HZLNUT 225</t>
+  </si>
+  <si>
+    <t>20115188</t>
+  </si>
+  <si>
+    <t>CMORY UHT ALMND 225</t>
+  </si>
+  <si>
+    <t>20104637</t>
+  </si>
+  <si>
+    <t>CIMORY UHT CSHEW 225</t>
+  </si>
+  <si>
+    <t>20099571</t>
+  </si>
+  <si>
     <t>CIMORY UHT CHOCO 225</t>
   </si>
   <si>
-    <t>20140794</t>
-  </si>
-  <si>
-    <t>CIMORY UHT MARIE 225</t>
-  </si>
-  <si>
-    <t>20140793</t>
-  </si>
-  <si>
-    <t>CIMORY UHT MTCHA 225</t>
-  </si>
-  <si>
-    <t>20122822</t>
-  </si>
-  <si>
-    <t>CMORY UHT MARIE 250</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20115187</t>
-  </si>
-  <si>
-    <t>CMORY UHT HZLNUT 250</t>
-  </si>
-  <si>
-    <t>20115188</t>
-  </si>
-  <si>
-    <t>CMORY UHT ALMND 250</t>
-  </si>
-  <si>
-    <t>20104637</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CSHEW 250</t>
-  </si>
-  <si>
-    <t>20099571</t>
-  </si>
-  <si>
-    <t>CIMORY UHT CHOCO 250</t>
-  </si>
-  <si>
     <t>20104636</t>
   </si>
   <si>
-    <t>CIMORY UHT CHOML 250</t>
+    <t>CIMORY UHT CHOML 225</t>
   </si>
   <si>
     <t>20129109</t>
   </si>
   <si>
-    <t>CIMORY CHO.TRMSU 250</t>
+    <t>CIMORY CHO.TRMSU 225</t>
   </si>
   <si>
     <t>20099572</t>
   </si>
   <si>
-    <t>CIMORY UHT STRAW 250</t>
+    <t>CIMORY UHT STRAW 225</t>
   </si>
   <si>
     <t>20134390</t>
   </si>
   <si>
-    <t>CIMORY BBS LKTSA 250</t>
+    <t>CIMORY BBS LKTSA 225</t>
   </si>
   <si>
     <t>20025753</t>
@@ -2056,13 +2050,13 @@
     <t>10007380</t>
   </si>
   <si>
-    <t>ULTRA SLIM COKLAT200</t>
+    <t>ULTRA SLIM CO 200 ML</t>
   </si>
   <si>
     <t>10008095</t>
   </si>
   <si>
-    <t>ULTRA SLIM STRAW 200</t>
+    <t>ULTRA SLIM ST 200 ML</t>
   </si>
   <si>
     <t>10007379</t>
@@ -2221,7 +2215,7 @@
     <t>20090527</t>
   </si>
   <si>
-    <t>CRYSTALIN BTL 600mL</t>
+    <t>CRYSTLN AIR B 600 ML</t>
   </si>
   <si>
     <t>20077499</t>
@@ -2305,7 +2299,7 @@
     <t>10004336</t>
   </si>
   <si>
-    <t>INDOMARET AIR MIN600</t>
+    <t>IDM MINERAL 600 ML</t>
   </si>
   <si>
     <t>46</t>
@@ -2728,7 +2722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F358"/>
+  <dimension ref="A1:F357"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -7592,18 +7586,18 @@
         <v>517</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>166</v>
+        <v>524</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>3</v>
@@ -7612,10 +7606,10 @@
         <v>517</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>526</v>
+        <v>33</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7632,10 +7626,10 @@
         <v>517</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
@@ -7652,10 +7646,10 @@
         <v>517</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -7672,7 +7666,7 @@
         <v>517</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>33</v>
@@ -7689,30 +7683,30 @@
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D249" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="B249" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="C249" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>537</v>
-      </c>
       <c r="E249" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>28</v>
@@ -7729,10 +7723,10 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>28</v>
@@ -7749,10 +7743,10 @@
         <v>3</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>28</v>
@@ -7769,13 +7763,13 @@
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -7789,13 +7783,13 @@
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -7809,10 +7803,10 @@
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>23</v>
@@ -7829,10 +7823,10 @@
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7849,30 +7843,30 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="B257" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="C257" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>554</v>
-      </c>
       <c r="E257" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>28</v>
@@ -7889,10 +7883,10 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>28</v>
@@ -7909,13 +7903,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -7929,13 +7923,13 @@
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
@@ -7949,10 +7943,10 @@
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>28</v>
@@ -7969,10 +7963,10 @@
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>28</v>
@@ -7989,10 +7983,10 @@
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>554</v>
+        <v>567</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>28</v>
@@ -8000,19 +7994,19 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D264" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="B264" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="C264" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D264" s="1" t="s">
-        <v>569</v>
-      </c>
       <c r="E264" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>28</v>
@@ -8029,10 +8023,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>28</v>
@@ -8049,10 +8043,10 @@
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>28</v>
@@ -8069,10 +8063,10 @@
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>28</v>
@@ -8089,10 +8083,10 @@
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>28</v>
@@ -8109,10 +8103,10 @@
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>28</v>
@@ -8129,10 +8123,10 @@
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>28</v>
@@ -8149,10 +8143,10 @@
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>28</v>
@@ -8169,10 +8163,10 @@
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>54</v>
+        <v>144</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>28</v>
@@ -8189,10 +8183,10 @@
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>569</v>
+        <v>588</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>28</v>
@@ -8200,22 +8194,22 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D274" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="B274" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="C274" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D274" s="1" t="s">
-        <v>590</v>
-      </c>
       <c r="E274" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -8229,13 +8223,13 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -8249,10 +8243,10 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>28</v>
@@ -8269,10 +8263,10 @@
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>28</v>
@@ -8289,10 +8283,10 @@
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>28</v>
@@ -8309,10 +8303,10 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>28</v>
@@ -8329,10 +8323,10 @@
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>28</v>
@@ -8349,10 +8343,10 @@
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>28</v>
@@ -8369,10 +8363,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>54</v>
+        <v>144</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>28</v>
@@ -8389,10 +8383,10 @@
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>28</v>
@@ -8409,10 +8403,10 @@
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>590</v>
+        <v>611</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>165</v>
+        <v>4</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>28</v>
@@ -8420,19 +8414,19 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D285" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="B285" s="1" t="s">
-        <v>612</v>
-      </c>
-      <c r="C285" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>613</v>
-      </c>
       <c r="E285" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>28</v>
@@ -8449,10 +8443,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>28</v>
@@ -8469,10 +8463,10 @@
         <v>3</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>28</v>
@@ -8489,10 +8483,10 @@
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>28</v>
@@ -8509,10 +8503,10 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>28</v>
@@ -8529,33 +8523,33 @@
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>28</v>
+        <v>624</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>626</v>
+        <v>28</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -8569,10 +8563,10 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>28</v>
@@ -8589,10 +8583,10 @@
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>54</v>
+        <v>144</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>28</v>
@@ -8609,33 +8603,33 @@
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>28</v>
+        <v>624</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
+        <v>634</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D295" s="1" t="s">
         <v>633</v>
       </c>
-      <c r="B295" s="1" t="s">
-        <v>634</v>
-      </c>
-      <c r="C295" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>635</v>
-      </c>
       <c r="E295" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8649,13 +8643,13 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
@@ -8669,13 +8663,13 @@
         <v>3</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -8689,13 +8683,13 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8709,13 +8703,13 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
@@ -8729,13 +8723,13 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
@@ -8749,13 +8743,13 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
@@ -8769,13 +8763,13 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
@@ -8789,30 +8783,30 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>635</v>
+        <v>652</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>626</v>
+        <v>28</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B304" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="C304" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D304" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="B304" s="1" t="s">
-        <v>653</v>
-      </c>
-      <c r="C304" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D304" s="1" t="s">
-        <v>654</v>
-      </c>
       <c r="E304" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>28</v>
@@ -8829,10 +8823,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>28</v>
@@ -8849,10 +8843,10 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>28</v>
@@ -8869,10 +8863,10 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>28</v>
@@ -8889,10 +8883,10 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>28</v>
@@ -8909,10 +8903,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>28</v>
@@ -8929,10 +8923,10 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>28</v>
@@ -8949,10 +8943,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>28</v>
@@ -8969,10 +8963,10 @@
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>654</v>
+        <v>671</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>28</v>
@@ -8980,19 +8974,19 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B313" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="C313" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D313" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="B313" s="1" t="s">
-        <v>672</v>
-      </c>
-      <c r="C313" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>673</v>
-      </c>
       <c r="E313" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>28</v>
@@ -9009,10 +9003,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>28</v>
@@ -9029,10 +9023,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>28</v>
@@ -9049,10 +9043,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>28</v>
@@ -9069,10 +9063,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>28</v>
@@ -9089,10 +9083,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>28</v>
@@ -9109,10 +9103,10 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>28</v>
@@ -9129,10 +9123,10 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>28</v>
@@ -9149,10 +9143,10 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>28</v>
@@ -9160,19 +9154,19 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="B322" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="C322" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D322" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="B322" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="C322" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D322" s="1" t="s">
-        <v>692</v>
-      </c>
       <c r="E322" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>28</v>
@@ -9189,10 +9183,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>28</v>
@@ -9209,10 +9203,10 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>28</v>
@@ -9229,10 +9223,10 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>28</v>
@@ -9249,10 +9243,10 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>28</v>
@@ -9269,10 +9263,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>28</v>
@@ -9289,10 +9283,10 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>28</v>
@@ -9309,10 +9303,10 @@
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>28</v>
@@ -9329,10 +9323,10 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>692</v>
+        <v>709</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>28</v>
@@ -9340,19 +9334,19 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D331" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="B331" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="C331" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>711</v>
-      </c>
       <c r="E331" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>28</v>
@@ -9369,13 +9363,13 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -9389,10 +9383,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>23</v>
@@ -9409,13 +9403,13 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -9429,10 +9423,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>28</v>
@@ -9449,10 +9443,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>28</v>
@@ -9469,10 +9463,10 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>28</v>
@@ -9489,10 +9483,10 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>28</v>
@@ -9509,10 +9503,10 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>54</v>
+        <v>144</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>28</v>
@@ -9529,33 +9523,33 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>711</v>
+        <v>730</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D341" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="B341" s="1" t="s">
-        <v>731</v>
-      </c>
-      <c r="C341" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>732</v>
-      </c>
       <c r="E341" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9569,13 +9563,13 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -9589,13 +9583,13 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -9609,13 +9603,13 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -9629,10 +9623,10 @@
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F345" s="1" t="s">
         <v>28</v>
@@ -9649,13 +9643,13 @@
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -9669,33 +9663,33 @@
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>23</v>
+        <v>745</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>747</v>
+        <v>33</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -9709,30 +9703,30 @@
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>732</v>
+        <v>750</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="C350" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D350" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="B350" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="C350" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D350" s="1" t="s">
-        <v>752</v>
-      </c>
       <c r="E350" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F350" s="1" t="s">
         <v>28</v>
@@ -9749,13 +9743,13 @@
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>28</v>
+        <v>166</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -9769,132 +9763,112 @@
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>752</v>
+        <v>757</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B353" s="1" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B354" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>33</v>
+        <v>764</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="B355" s="1" t="s">
-        <v>764</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>765</v>
-      </c>
       <c r="E355" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B356" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B357" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F357" s="1" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A358" s="1" t="s">
-        <v>773</v>
-      </c>
-      <c r="B358" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="C358" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D358" s="1" t="s">
-        <v>765</v>
-      </c>
-      <c r="E358" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F358" s="1" t="s">
         <v>28</v>
       </c>
     </row>

--- a/CLB07N.xlsx
+++ b/CLB07N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2142" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2154" uniqueCount="778">
   <si>
     <t/>
   </si>
@@ -115,6 +115,21 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
+    <t>20046315</t>
+  </si>
+  <si>
+    <t>MINUTE M. NB STRW300</t>
+  </si>
+  <si>
+    <t>20046314</t>
+  </si>
+  <si>
+    <t>MINUTE M. NB ORG 300</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>20065778</t>
   </si>
   <si>
@@ -157,9 +172,6 @@
     <t>SPRITE NIPIS MINT390</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>20137093</t>
   </si>
   <si>
@@ -214,6 +226,21 @@
     <t>TEBS SPRK MIX FRT330</t>
   </si>
   <si>
+    <t>20045995</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK STRO 238</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20045996</t>
+  </si>
+  <si>
+    <t>KAKI3 ANAK LECI 238</t>
+  </si>
+  <si>
     <t>10037437</t>
   </si>
   <si>
@@ -244,9 +271,6 @@
     <t>KAKI3 PENY.LECI 320</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
     <t>20037150</t>
   </si>
   <si>
@@ -259,10 +283,10 @@
     <t>KAKI TIGA STRO 320ML</t>
   </si>
   <si>
-    <t>20045995</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK STRO 238</t>
+    <t>20122090</t>
+  </si>
+  <si>
+    <t>ADEM/S MD LMN TEA350</t>
   </si>
   <si>
     <t>20053540</t>
@@ -271,12 +295,6 @@
     <t>ADEM SARI CK BTL 350</t>
   </si>
   <si>
-    <t>20122090</t>
-  </si>
-  <si>
-    <t>ADEM/S MD LMN TEA350</t>
-  </si>
-  <si>
     <t>20083775</t>
   </si>
   <si>
@@ -295,6 +313,15 @@
     <t>ADEMSARI CK SPRK 320</t>
   </si>
   <si>
+    <t>20144234</t>
+  </si>
+  <si>
+    <t>ADM SR C/K GUAVA 320</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
     <t>20069199</t>
   </si>
   <si>
@@ -307,22 +334,16 @@
     <t>KK3 CLTPIA ML/ORG320</t>
   </si>
   <si>
-    <t>20045996</t>
-  </si>
-  <si>
-    <t>KAKI3 ANAK LECI 238</t>
-  </si>
-  <si>
-    <t>20046315</t>
-  </si>
-  <si>
-    <t>MINUTE M. NB STRW300</t>
-  </si>
-  <si>
-    <t>20046314</t>
-  </si>
-  <si>
-    <t>MINUTE M. NB ORG 300</t>
+    <t>20102789</t>
+  </si>
+  <si>
+    <t>ABC CHOCMLT COFF 180</t>
+  </si>
+  <si>
+    <t>20102790</t>
+  </si>
+  <si>
+    <t>ABC MILK COFFEE 180</t>
   </si>
   <si>
     <t>20120499</t>
@@ -349,40 +370,40 @@
     <t>LUWAK KOPI+GULA 220</t>
   </si>
   <si>
+    <t>20123322</t>
+  </si>
+  <si>
+    <t>GOLDA CAPPUCCINO 200</t>
+  </si>
+  <si>
+    <t>20087542</t>
+  </si>
+  <si>
+    <t>GOLDA COFF.DOLCE 200</t>
+  </si>
+  <si>
+    <t>20143270</t>
+  </si>
+  <si>
+    <t>GOLDA AREN LATTE 200</t>
+  </si>
+  <si>
     <t>20078206</t>
   </si>
   <si>
     <t>LUWAK WHT ORGL 220ML</t>
   </si>
   <si>
-    <t>20123322</t>
-  </si>
-  <si>
-    <t>GOLDA CAPPUCCINO 200</t>
-  </si>
-  <si>
-    <t>20087542</t>
-  </si>
-  <si>
-    <t>GOLDA COFF.DOLCE 200</t>
-  </si>
-  <si>
-    <t>20143270</t>
-  </si>
-  <si>
-    <t>GOLDA AREN LATTE 200</t>
-  </si>
-  <si>
-    <t>20102789</t>
-  </si>
-  <si>
-    <t>ABC CHOCMLT COFF 180</t>
-  </si>
-  <si>
-    <t>20102790</t>
-  </si>
-  <si>
-    <t>ABC MILK COFFEE 180</t>
+    <t>20109969</t>
+  </si>
+  <si>
+    <t>KOPIKO LUCKY DAY 180</t>
+  </si>
+  <si>
+    <t>20045415</t>
+  </si>
+  <si>
+    <t>KOPIKO 78C 240ML</t>
   </si>
   <si>
     <t>20120904</t>
@@ -448,18 +469,6 @@
     <t>10</t>
   </si>
   <si>
-    <t>20045415</t>
-  </si>
-  <si>
-    <t>KOPIKO 78C 240ML</t>
-  </si>
-  <si>
-    <t>20109969</t>
-  </si>
-  <si>
-    <t>KOPIKO LUCKY DAY 180</t>
-  </si>
-  <si>
     <t>20076770</t>
   </si>
   <si>
@@ -511,9 +520,6 @@
     <t>11</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
     <t>20139578</t>
   </si>
   <si>
@@ -706,25 +712,25 @@
     <t>20002203</t>
   </si>
   <si>
-    <t>SOSRO F.TEA APEL 500</t>
+    <t>SOSRO F.TEA APEL 450</t>
   </si>
   <si>
     <t>20003698</t>
   </si>
   <si>
-    <t>SOSRO FR.TEA XTRM500</t>
+    <t>SOSRO FR.TEA XTRM450</t>
   </si>
   <si>
     <t>20002205</t>
   </si>
   <si>
-    <t>SOSRO F.TEA BLKCR500</t>
+    <t>SOSRO F.TEA BLKCR450</t>
   </si>
   <si>
     <t>20134046</t>
   </si>
   <si>
-    <t>FRUIT TEA FREEZE 500</t>
+    <t>FRUIT TEA FREEZE 450</t>
   </si>
   <si>
     <t>20126464</t>
@@ -980,6 +986,15 @@
   </si>
   <si>
     <t>FRESTEA GRN MADU 500</t>
+  </si>
+  <si>
+    <t>20140263</t>
+  </si>
+  <si>
+    <t>FRESTEA BLCKCRNT 500</t>
+  </si>
+  <si>
+    <t>PT,(E-14H)</t>
   </si>
   <si>
     <t>20012574</t>
@@ -2722,7 +2737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F357"/>
+  <dimension ref="A1:F359"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2983,10 +2998,10 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -3003,10 +3018,10 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -3014,10 +3029,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -3026,7 +3041,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -3034,10 +3049,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -3046,7 +3061,7 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -3054,10 +3069,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -3066,7 +3081,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -3074,10 +3089,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -3086,7 +3101,7 @@
         <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -3094,10 +3109,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -3106,7 +3121,7 @@
         <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -3126,7 +3141,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -3134,10 +3149,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -3146,7 +3161,7 @@
         <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -3154,19 +3169,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -3174,22 +3189,22 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F23" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -3206,10 +3221,10 @@
         <v>14</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -3226,7 +3241,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>28</v>
@@ -3246,10 +3261,10 @@
         <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -3266,7 +3281,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>28</v>
@@ -3283,10 +3298,10 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>33</v>
@@ -3303,13 +3318,13 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3323,41 +3338,41 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -3366,10 +3381,10 @@
         <v>17</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3386,10 +3401,10 @@
         <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3406,10 +3421,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3426,10 +3441,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3443,13 +3458,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3463,13 +3478,13 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F37" s="1" t="s">
-        <v>33</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3483,13 +3498,13 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3506,10 +3521,10 @@
         <v>20</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3526,7 +3541,7 @@
         <v>20</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>28</v>
@@ -3546,10 +3561,10 @@
         <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3566,10 +3581,10 @@
         <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3586,10 +3601,10 @@
         <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3603,130 +3618,130 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>23</v>
@@ -3734,19 +3749,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>28</v>
@@ -3754,39 +3769,39 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>28</v>
@@ -3794,79 +3809,79 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>28</v>
@@ -3874,19 +3889,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>28</v>
@@ -3894,19 +3909,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>28</v>
@@ -3914,19 +3929,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>28</v>
@@ -3934,19 +3949,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>28</v>
@@ -3954,19 +3969,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>28</v>
@@ -3974,19 +3989,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>28</v>
@@ -3994,19 +4009,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>28</v>
@@ -4014,19 +4029,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>144</v>
+        <v>38</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>28</v>
@@ -4043,10 +4058,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>28</v>
@@ -4063,10 +4078,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>28</v>
@@ -4083,30 +4098,30 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="E69" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>23</v>
@@ -4114,19 +4129,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>23</v>
@@ -4134,19 +4149,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>23</v>
@@ -4154,19 +4169,19 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>23</v>
@@ -4174,39 +4189,39 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>28</v>
@@ -4214,42 +4229,42 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -4263,13 +4278,13 @@
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -4283,13 +4298,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -4303,10 +4318,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>28</v>
@@ -4323,13 +4338,13 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -4343,13 +4358,13 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -4363,30 +4378,30 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="E83" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>23</v>
@@ -4403,10 +4418,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>23</v>
@@ -4423,13 +4438,13 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4443,13 +4458,13 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -4463,10 +4478,10 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>23</v>
@@ -4483,10 +4498,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>23</v>
@@ -4503,10 +4518,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>23</v>
@@ -4523,13 +4538,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4543,10 +4558,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>28</v>
@@ -4563,30 +4578,30 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>151</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>33</v>
@@ -4603,13 +4618,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4623,13 +4638,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4643,10 +4658,10 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>28</v>
@@ -4663,13 +4678,13 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -4683,13 +4698,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -4703,10 +4718,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>28</v>
@@ -4723,13 +4738,13 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4743,10 +4758,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -4763,30 +4778,30 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>151</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>28</v>
@@ -4803,10 +4818,10 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>28</v>
@@ -4823,10 +4838,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>28</v>
@@ -4843,10 +4858,10 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>28</v>
@@ -4863,10 +4878,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>28</v>
@@ -4883,10 +4898,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>28</v>
@@ -4903,10 +4918,10 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>28</v>
@@ -4923,33 +4938,33 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B111" s="1" t="s">
+      <c r="C111" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C111" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>240</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -4963,13 +4978,13 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -4983,13 +4998,13 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -5003,10 +5018,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>28</v>
@@ -5023,10 +5038,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>28</v>
@@ -5043,10 +5058,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>28</v>
@@ -5063,10 +5078,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>28</v>
@@ -5083,10 +5098,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>28</v>
@@ -5103,10 +5118,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>28</v>
@@ -5114,19 +5129,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>28</v>
@@ -5143,10 +5158,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>28</v>
@@ -5163,10 +5178,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>28</v>
@@ -5183,10 +5198,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>28</v>
@@ -5203,10 +5218,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>28</v>
@@ -5223,10 +5238,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>28</v>
@@ -5243,10 +5258,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>28</v>
@@ -5263,50 +5278,50 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>276</v>
+        <v>28</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F128" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B129" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="C129" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>279</v>
-      </c>
       <c r="E129" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>28</v>
@@ -5323,10 +5338,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>28</v>
@@ -5343,10 +5358,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>28</v>
@@ -5363,10 +5378,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>28</v>
@@ -5374,19 +5389,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B133" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="C133" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C133" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="E133" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>28</v>
@@ -5403,10 +5418,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>28</v>
@@ -5423,10 +5438,10 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>28</v>
@@ -5443,10 +5458,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>28</v>
@@ -5463,10 +5478,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>28</v>
@@ -5483,10 +5498,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>28</v>
@@ -5503,10 +5518,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>28</v>
@@ -5514,19 +5529,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>28</v>
@@ -5543,10 +5558,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>28</v>
@@ -5563,10 +5578,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>28</v>
@@ -5583,10 +5598,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>28</v>
@@ -5603,10 +5618,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>28</v>
@@ -5623,13 +5638,13 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -5643,10 +5658,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>33</v>
@@ -5663,33 +5678,33 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B148" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="B148" s="1" t="s">
+      <c r="C148" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="C148" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>320</v>
-      </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -5703,10 +5718,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>5</v>
@@ -5723,50 +5738,50 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>28</v>
+        <v>327</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>28</v>
@@ -5774,19 +5789,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>28</v>
@@ -5794,39 +5809,39 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>28</v>
@@ -5843,13 +5858,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5863,10 +5878,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>28</v>
@@ -5874,19 +5889,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>28</v>
@@ -5894,59 +5909,59 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>23</v>
@@ -5954,59 +5969,59 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>28</v>
@@ -6023,10 +6038,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>28</v>
@@ -6043,30 +6058,30 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B167" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="E167" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>28</v>
@@ -6074,39 +6089,39 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>28</v>
@@ -6114,19 +6129,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>28</v>
@@ -6134,19 +6149,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>28</v>
@@ -6154,19 +6169,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>28</v>
@@ -6174,19 +6189,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>28</v>
@@ -6203,10 +6218,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>28</v>
@@ -6223,10 +6238,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>28</v>
@@ -6234,19 +6249,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B176" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D176" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E176" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>28</v>
@@ -6254,19 +6269,19 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>28</v>
@@ -6274,19 +6289,19 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>28</v>
@@ -6294,19 +6309,19 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>28</v>
@@ -6314,22 +6329,22 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -6343,10 +6358,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>28</v>
@@ -6363,33 +6378,33 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B183" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>390</v>
-      </c>
       <c r="E183" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>397</v>
+        <v>28</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -6403,13 +6418,13 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>397</v>
+        <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -6423,73 +6438,73 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>28</v>
+        <v>402</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E186" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F186" s="1" t="s">
         <v>402</v>
-      </c>
-      <c r="B186" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C186" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F186" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6503,13 +6518,13 @@
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -6523,150 +6538,150 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B191" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C191" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="E191" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>28</v>
@@ -6683,10 +6698,10 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>28</v>
@@ -6703,10 +6718,10 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>28</v>
@@ -6714,19 +6729,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B200" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="E200" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>28</v>
@@ -6734,19 +6749,19 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>28</v>
@@ -6754,19 +6769,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>28</v>
@@ -6774,19 +6789,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>28</v>
@@ -6794,19 +6809,19 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>28</v>
@@ -6814,19 +6829,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>28</v>
@@ -6834,19 +6849,19 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>28</v>
@@ -6854,19 +6869,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>28</v>
@@ -6883,10 +6898,10 @@
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>28</v>
@@ -6903,10 +6918,10 @@
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>28</v>
@@ -6914,19 +6929,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B210" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="C210" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>448</v>
-      </c>
       <c r="E210" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>28</v>
@@ -6934,19 +6949,19 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>28</v>
@@ -6954,19 +6969,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>28</v>
@@ -6974,19 +6989,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>28</v>
@@ -6994,19 +7009,19 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>28</v>
@@ -7014,39 +7029,39 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>28</v>
@@ -7063,13 +7078,13 @@
         <v>3</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -7083,10 +7098,10 @@
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>28</v>
@@ -7094,19 +7109,19 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="B219" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>467</v>
-      </c>
       <c r="E219" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>28</v>
@@ -7114,19 +7129,19 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>28</v>
@@ -7134,19 +7149,19 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>28</v>
@@ -7154,19 +7169,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>28</v>
@@ -7174,82 +7189,82 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="B226" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="B226" s="1" t="s">
-        <v>487</v>
-      </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>485</v>
+        <v>472</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -7263,10 +7278,10 @@
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>28</v>
@@ -7274,19 +7289,19 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D228" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="B228" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="C228" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D228" s="1" t="s">
-        <v>485</v>
-      </c>
       <c r="E228" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F228" s="1" t="s">
         <v>28</v>
@@ -7294,102 +7309,102 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>166</v>
+        <v>23</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -7403,13 +7418,13 @@
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
@@ -7423,10 +7438,10 @@
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>23</v>
@@ -7434,19 +7449,19 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D236" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="B236" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="C236" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>502</v>
-      </c>
       <c r="E236" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>23</v>
@@ -7454,19 +7469,19 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>23</v>
@@ -7474,62 +7489,62 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
@@ -7543,13 +7558,13 @@
         <v>3</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -7563,10 +7578,10 @@
         <v>3</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F242" s="1" t="s">
         <v>23</v>
@@ -7574,22 +7589,22 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D243" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="B243" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="C243" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>517</v>
-      </c>
       <c r="E243" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>524</v>
+        <v>23</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
@@ -7603,13 +7618,13 @@
         <v>3</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -7623,30 +7638,30 @@
         <v>3</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>28</v>
+        <v>529</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F246" s="1" t="s">
         <v>33</v>
@@ -7654,42 +7669,42 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -7703,13 +7718,13 @@
         <v>3</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
@@ -7723,10 +7738,10 @@
         <v>3</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F250" s="1" t="s">
         <v>28</v>
@@ -7734,19 +7749,19 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D251" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="B251" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="C251" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D251" s="1" t="s">
-        <v>535</v>
-      </c>
       <c r="E251" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>28</v>
@@ -7754,79 +7769,79 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>23</v>
@@ -7834,22 +7849,22 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -7863,13 +7878,13 @@
         <v>3</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
@@ -7883,10 +7898,10 @@
         <v>3</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>28</v>
@@ -7894,39 +7909,39 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D259" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="B259" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="C259" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D259" s="1" t="s">
-        <v>552</v>
-      </c>
       <c r="E259" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>28</v>
@@ -7934,39 +7949,39 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>28</v>
@@ -7974,19 +7989,19 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>28</v>
@@ -8003,10 +8018,10 @@
         <v>3</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F264" s="1" t="s">
         <v>28</v>
@@ -8023,10 +8038,10 @@
         <v>3</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>28</v>
@@ -8034,19 +8049,19 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D266" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="B266" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="C266" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D266" s="1" t="s">
-        <v>567</v>
-      </c>
       <c r="E266" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>28</v>
@@ -8054,19 +8069,19 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>28</v>
@@ -8074,19 +8089,19 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>28</v>
@@ -8094,19 +8109,19 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>28</v>
@@ -8114,19 +8129,19 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>28</v>
@@ -8134,19 +8149,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>28</v>
@@ -8154,19 +8169,19 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>567</v>
+        <v>572</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>28</v>
@@ -8174,19 +8189,19 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>28</v>
@@ -8203,13 +8218,13 @@
         <v>3</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>588</v>
+        <v>572</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
@@ -8223,10 +8238,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>28</v>
@@ -8234,39 +8249,39 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D276" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="B276" s="1" t="s">
-        <v>594</v>
-      </c>
-      <c r="C276" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>588</v>
-      </c>
       <c r="E276" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F277" s="1" t="s">
         <v>28</v>
@@ -8274,19 +8289,19 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>28</v>
@@ -8294,19 +8309,19 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F279" s="1" t="s">
         <v>28</v>
@@ -8314,19 +8329,19 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>28</v>
@@ -8334,19 +8349,19 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>28</v>
@@ -8354,19 +8369,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>28</v>
@@ -8374,19 +8389,19 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>588</v>
+        <v>593</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>165</v>
+        <v>58</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>28</v>
@@ -8394,19 +8409,19 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>4</v>
+        <v>151</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>28</v>
@@ -8423,10 +8438,10 @@
         <v>3</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>611</v>
+        <v>593</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>8</v>
+        <v>168</v>
       </c>
       <c r="F285" s="1" t="s">
         <v>28</v>
@@ -8443,10 +8458,10 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>28</v>
@@ -8454,19 +8469,19 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D287" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="B287" s="1" t="s">
-        <v>617</v>
-      </c>
-      <c r="C287" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D287" s="1" t="s">
-        <v>611</v>
-      </c>
       <c r="E287" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>28</v>
@@ -8474,19 +8489,19 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>28</v>
@@ -8494,19 +8509,19 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F289" s="1" t="s">
         <v>28</v>
@@ -8514,22 +8529,22 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>624</v>
+        <v>28</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -8543,10 +8558,10 @@
         <v>3</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>28</v>
@@ -8563,30 +8578,30 @@
         <v>3</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>28</v>
+        <v>629</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>28</v>
@@ -8594,22 +8609,22 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>624</v>
+        <v>28</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -8623,13 +8638,13 @@
         <v>3</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>624</v>
+        <v>28</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
@@ -8643,153 +8658,153 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D297" s="1" t="s">
         <v>638</v>
       </c>
-      <c r="B297" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="C297" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D297" s="1" t="s">
-        <v>633</v>
-      </c>
       <c r="E297" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B299" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B300" s="1" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B301" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>633</v>
+        <v>638</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>624</v>
+        <v>629</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>28</v>
+        <v>629</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
@@ -8803,13 +8818,13 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>652</v>
+        <v>638</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>28</v>
+        <v>629</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
@@ -8823,10 +8838,10 @@
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>28</v>
@@ -8834,19 +8849,19 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B306" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="C306" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D306" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="B306" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="C306" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>652</v>
-      </c>
       <c r="E306" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F306" s="1" t="s">
         <v>28</v>
@@ -8854,19 +8869,19 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F307" s="1" t="s">
         <v>28</v>
@@ -8874,19 +8889,19 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F308" s="1" t="s">
         <v>28</v>
@@ -8894,19 +8909,19 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>28</v>
@@ -8914,19 +8929,19 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F310" s="1" t="s">
         <v>28</v>
@@ -8934,19 +8949,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>28</v>
@@ -8954,19 +8969,19 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>28</v>
@@ -8983,10 +8998,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>671</v>
+        <v>657</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>28</v>
@@ -9003,10 +9018,10 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>28</v>
@@ -9014,19 +9029,19 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B315" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="C315" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D315" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="B315" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="C315" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D315" s="1" t="s">
-        <v>671</v>
-      </c>
       <c r="E315" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>28</v>
@@ -9034,19 +9049,19 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>28</v>
@@ -9054,19 +9069,19 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>28</v>
@@ -9074,19 +9089,19 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>28</v>
@@ -9094,19 +9109,19 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>28</v>
@@ -9114,19 +9129,19 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>28</v>
@@ -9134,19 +9149,19 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>28</v>
@@ -9163,10 +9178,10 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>690</v>
+        <v>676</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>28</v>
@@ -9183,10 +9198,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>28</v>
@@ -9194,19 +9209,19 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="B324" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="C324" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D324" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="B324" s="1" t="s">
-        <v>696</v>
-      </c>
-      <c r="C324" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D324" s="1" t="s">
-        <v>690</v>
-      </c>
       <c r="E324" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F324" s="1" t="s">
         <v>28</v>
@@ -9214,19 +9229,19 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F325" s="1" t="s">
         <v>28</v>
@@ -9234,19 +9249,19 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>28</v>
@@ -9254,19 +9269,19 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>28</v>
@@ -9274,19 +9289,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F328" s="1" t="s">
         <v>28</v>
@@ -9294,19 +9309,19 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>28</v>
@@ -9314,19 +9329,19 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>28</v>
@@ -9343,10 +9358,10 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F331" s="1" t="s">
         <v>28</v>
@@ -9363,90 +9378,90 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="B333" s="1" t="s">
-        <v>715</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="E333" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F333" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B334" s="1" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B335" s="1" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B336" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>28</v>
@@ -9454,19 +9469,19 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>28</v>
@@ -9474,19 +9489,19 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>28</v>
@@ -9494,19 +9509,19 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>144</v>
+        <v>55</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>28</v>
@@ -9514,22 +9529,22 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>730</v>
+        <v>714</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
@@ -9543,13 +9558,13 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>730</v>
+        <v>714</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="F341" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
@@ -9563,30 +9578,30 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C343" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D343" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="B343" s="1" t="s">
-        <v>736</v>
-      </c>
-      <c r="C343" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D343" s="1" t="s">
-        <v>730</v>
-      </c>
       <c r="E343" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>23</v>
@@ -9594,19 +9609,19 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B344" s="1" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F344" s="1" t="s">
         <v>28</v>
@@ -9614,62 +9629,62 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B345" s="1" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B346" s="1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>745</v>
+        <v>28</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -9683,13 +9698,13 @@
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>730</v>
+        <v>735</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -9703,13 +9718,13 @@
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="E349" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F349" s="1" t="s">
         <v>750</v>
-      </c>
-      <c r="E349" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F349" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -9723,13 +9738,13 @@
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -9743,30 +9758,30 @@
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>750</v>
+        <v>755</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="C352" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D352" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="B352" s="1" t="s">
-        <v>756</v>
-      </c>
-      <c r="C352" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D352" s="1" t="s">
-        <v>757</v>
-      </c>
       <c r="E352" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F352" s="1" t="s">
         <v>28</v>
@@ -9783,92 +9798,132 @@
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B354" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="B354" s="1" t="s">
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
         <v>762</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>763</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>764</v>
+        <v>28</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="B355" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>763</v>
-      </c>
       <c r="E355" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>767</v>
+        <v>33</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="C356" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D356" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="B356" s="1" t="s">
+      <c r="E356" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F356" s="1" t="s">
         <v>769</v>
-      </c>
-      <c r="C356" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D356" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="E356" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F356" s="1" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="B357" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="B357" s="1" t="s">
+      <c r="C357" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="E357" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F357" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="C357" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D357" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="E357" s="1" t="s">
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="C358" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="E358" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F358" s="1" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="E359" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F357" s="1" t="s">
+      <c r="F359" s="1" t="s">
         <v>28</v>
       </c>
     </row>
